--- a/excel/PR. 3 Final Project/PR. 3 Final Project (1).xlsx
+++ b/excel/PR. 3 Final Project/PR. 3 Final Project (1).xlsx
@@ -5,12 +5,12 @@
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\my\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\my\excel\PR. 3 Final Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F944EA02-CD88-46E9-9F5B-3F8648D8B536}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{651330D2-B549-49BA-988C-7DF9C4AAB8CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project Instructions" sheetId="1" r:id="rId1"/>
@@ -82,7 +82,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2392" uniqueCount="675">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2388" uniqueCount="675">
   <si>
     <t>PR. Final Project - "Data Intelligence Dashboard"</t>
   </si>
@@ -2483,7 +2483,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2571,6 +2571,7 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2841,47 +2842,23 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Pivot table and chart'!$B$4:$B$9</c:f>
+              <c:f>'Pivot table and chart'!$B$4:$B$5</c:f>
               <c:strCache>
-                <c:ptCount val="5"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Central</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>East</c:v>
-                </c:pt>
-                <c:pt idx="2">
                   <c:v>North</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>South</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>West</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Pivot table and chart'!$C$4:$C$9</c:f>
+              <c:f>'Pivot table and chart'!$C$4:$C$5</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>41288.340000000018</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>59288.389999999992</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>50808.310000000012</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>36398.750000000007</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>41408.680000000015</c:v>
+                  <c:v>50808.31</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3370,13 +3347,13 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>8338.7399999999961</c:v>
+                  <c:v>1119.8399999999999</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>171756.05000000013</c:v>
+                  <c:v>39239.040000000008</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>49097.680000000015</c:v>
+                  <c:v>10449.429999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3728,34 +3705,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>5219.1299999999974</c:v>
+                  <c:v>479.92</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>15298.979999999994</c:v>
+                  <c:v>4949.67</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3119.6099999999992</c:v>
+                  <c:v>639.91999999999996</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>23399.22</c:v>
+                  <c:v>2099.9300000000003</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>7049.5299999999988</c:v>
+                  <c:v>1949.8700000000001</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>8009.1099999999969</c:v>
+                  <c:v>1889.7900000000002</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>67499.25</c:v>
+                  <c:v>12599.859999999999</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>21999.119999999999</c:v>
+                  <c:v>5999.76</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>10399.479999999998</c:v>
+                  <c:v>3399.8300000000004</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>67199.039999999994</c:v>
+                  <c:v>16799.759999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4128,40 +4105,40 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>25799.15</c:v>
+                  <c:v>4599.8899999999994</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>16069.379999999997</c:v>
+                  <c:v>1749.92</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>19899.379999999997</c:v>
+                  <c:v>5649.9299999999994</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>27899.160000000007</c:v>
+                  <c:v>9969.5999999999985</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>17039.349999999999</c:v>
+                  <c:v>2129.87</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>19299.45</c:v>
+                  <c:v>89.99</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>18479.399999999994</c:v>
+                  <c:v>3919.8199999999997</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>15759.429999999997</c:v>
+                  <c:v>5539.8</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>12989.509999999997</c:v>
+                  <c:v>3869.88</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>20609.52</c:v>
+                  <c:v>4369.88</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>12309.439999999999</c:v>
+                  <c:v>2969.83</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>23039.3</c:v>
+                  <c:v>5949.9</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4677,47 +4654,23 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Pivot table and chart'!$B$4:$B$9</c:f>
+              <c:f>'Pivot table and chart'!$B$4:$B$5</c:f>
               <c:strCache>
-                <c:ptCount val="5"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Central</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>East</c:v>
-                </c:pt>
-                <c:pt idx="2">
                   <c:v>North</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>South</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>West</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Pivot table and chart'!$C$4:$C$9</c:f>
+              <c:f>'Pivot table and chart'!$C$4:$C$5</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>41288.340000000018</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>59288.389999999992</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>50808.310000000012</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>36398.750000000007</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>41408.680000000015</c:v>
+                  <c:v>50808.31</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5486,13 +5439,13 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>8338.7399999999961</c:v>
+                  <c:v>1119.8399999999999</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>171756.05000000013</c:v>
+                  <c:v>39239.040000000008</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>49097.680000000015</c:v>
+                  <c:v>10449.429999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6071,40 +6024,40 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>25799.15</c:v>
+                  <c:v>4599.8899999999994</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>16069.379999999997</c:v>
+                  <c:v>1749.92</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>19899.379999999997</c:v>
+                  <c:v>5649.9299999999994</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>27899.160000000007</c:v>
+                  <c:v>9969.5999999999985</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>17039.349999999999</c:v>
+                  <c:v>2129.87</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>19299.45</c:v>
+                  <c:v>89.99</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>18479.399999999994</c:v>
+                  <c:v>3919.8199999999997</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>15759.429999999997</c:v>
+                  <c:v>5539.8</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>12989.509999999997</c:v>
+                  <c:v>3869.88</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>20609.52</c:v>
+                  <c:v>4369.88</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>12309.439999999999</c:v>
+                  <c:v>2969.83</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>23039.3</c:v>
+                  <c:v>5949.9</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6652,34 +6605,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>5219.1299999999974</c:v>
+                  <c:v>479.92</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>15298.979999999994</c:v>
+                  <c:v>4949.67</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3119.6099999999992</c:v>
+                  <c:v>639.91999999999996</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>23399.22</c:v>
+                  <c:v>2099.9300000000003</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>7049.5299999999988</c:v>
+                  <c:v>1949.8700000000001</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>8009.1099999999969</c:v>
+                  <c:v>1889.7900000000002</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>67499.25</c:v>
+                  <c:v>12599.859999999999</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>21999.119999999999</c:v>
+                  <c:v>5999.76</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>10399.479999999998</c:v>
+                  <c:v>3399.8300000000004</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>67199.039999999994</c:v>
+                  <c:v>16799.759999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -17535,11 +17488,11 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0">
       <items count="6">
-        <item x="0"/>
-        <item x="4"/>
+        <item h="1" x="0"/>
+        <item h="1" x="4"/>
         <item x="2"/>
-        <item x="1"/>
-        <item x="3"/>
+        <item h="1" x="1"/>
+        <item h="1" x="3"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -18175,11 +18128,11 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0">
       <items count="6">
-        <item x="0"/>
-        <item x="4"/>
+        <item h="1" x="0"/>
+        <item h="1" x="4"/>
         <item x="2"/>
-        <item x="1"/>
-        <item x="3"/>
+        <item h="1" x="1"/>
+        <item h="1" x="3"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -18549,7 +18502,7 @@
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{14961EC1-8D90-46C7-A77F-E294CB2EE04B}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="14">
-  <location ref="B3:C9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <location ref="B3:C5" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="17">
     <pivotField showAll="0"/>
     <pivotField numFmtId="164" showAll="0">
@@ -18729,11 +18682,11 @@
     <pivotField showAll="0"/>
     <pivotField axis="axisRow" showAll="0">
       <items count="6">
-        <item x="0"/>
-        <item x="4"/>
+        <item h="1" x="0"/>
+        <item h="1" x="4"/>
         <item x="2"/>
-        <item x="1"/>
-        <item x="3"/>
+        <item h="1" x="1"/>
+        <item h="1" x="3"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -19010,21 +18963,9 @@
   <rowFields count="1">
     <field x="10"/>
   </rowFields>
-  <rowItems count="6">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
+  <rowItems count="2">
     <i>
       <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
     </i>
     <i t="grand">
       <x/>
@@ -19257,11 +19198,11 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0">
       <items count="6">
-        <item x="0"/>
-        <item x="4"/>
+        <item h="1" x="0"/>
+        <item h="1" x="4"/>
         <item x="2"/>
-        <item x="1"/>
-        <item x="3"/>
+        <item h="1" x="1"/>
+        <item h="1" x="3"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -19718,11 +19659,11 @@
   <data>
     <tabular pivotCacheId="709354815">
       <items count="5">
-        <i x="0" s="1"/>
-        <i x="4" s="1"/>
+        <i x="0"/>
+        <i x="4"/>
         <i x="2" s="1"/>
-        <i x="1" s="1"/>
-        <i x="3" s="1"/>
+        <i x="1"/>
+        <i x="3"/>
       </items>
     </tabular>
   </data>
@@ -47158,7 +47099,7 @@
       </c>
       <c r="W2" s="19">
         <f ca="1">TODAY()</f>
-        <v>46075</v>
+        <v>46078</v>
       </c>
       <c r="X2" s="30"/>
       <c r="Y2" s="18">
@@ -47238,7 +47179,7 @@
       </c>
       <c r="W3" s="20">
         <f ca="1">NOW()</f>
-        <v>46075.360446296298</v>
+        <v>46078.452847569446</v>
       </c>
     </row>
     <row r="4" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
@@ -63074,757 +63015,758 @@
   <dimension ref="A2:C51"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="31.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16" style="12" customWidth="1"/>
+    <col min="2" max="2" width="31.33203125" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.5546875" style="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="str" cm="1">
+      <c r="A2" s="12" t="str" cm="1">
         <f t="array" ref="A2:A51">_xlfn.UNIQUE('Final Project Dataset'!D2:D251)</f>
         <v>Paul Baker</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="12">
         <f>SUMIFS('Final Project Dataset'!N:N,
         'Final Project Dataset'!D:D,
         A2)</f>
         <v>8309.739999999998</v>
       </c>
-      <c r="C2" t="str">
+      <c r="C2" s="12" t="str">
         <f>IF(B2&gt;10000,"High Value","Normal")</f>
         <v>Normal</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="str">
+      <c r="A3" s="12" t="str">
         <v>Joseph Jackson</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="12">
         <f>SUMIFS('Final Project Dataset'!N:N,
         'Final Project Dataset'!D:D,
         A3)</f>
         <v>6949.84</v>
       </c>
-      <c r="C3" t="str">
+      <c r="C3" s="12" t="str">
         <f t="shared" ref="C3:C51" si="0">IF(B3&gt;10000,"High Value","Normal")</f>
         <v>Normal</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="str">
+      <c r="A4" s="12" t="str">
         <v>Kevin Scott</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="12">
         <f>SUMIFS('Final Project Dataset'!N:N,
         'Final Project Dataset'!D:D,
         A4)</f>
         <v>3259.87</v>
       </c>
-      <c r="C4" t="str">
+      <c r="C4" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Normal</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="str">
+      <c r="A5" s="12" t="str">
         <v>Kathleen Bennett</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="12">
         <f>SUMIFS('Final Project Dataset'!N:N,
         'Final Project Dataset'!D:D,
         A5)</f>
         <v>4309.8099999999995</v>
       </c>
-      <c r="C5" t="str">
+      <c r="C5" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Normal</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="str">
+      <c r="A6" s="12" t="str">
         <v>Michael Brown</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="12">
         <f>SUMIFS('Final Project Dataset'!N:N,
         'Final Project Dataset'!D:D,
         A6)</f>
         <v>6169.7400000000007</v>
       </c>
-      <c r="C6" t="str">
+      <c r="C6" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Normal</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="str">
+      <c r="A7" s="12" t="str">
         <v>Dorothy Nelson</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="12">
         <f>SUMIFS('Final Project Dataset'!N:N,
         'Final Project Dataset'!D:D,
         A7)</f>
         <v>8269.7900000000009</v>
       </c>
-      <c r="C7" t="str">
+      <c r="C7" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Normal</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="str">
+      <c r="A8" s="12" t="str">
         <v>Charles Allen</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="12">
         <f>SUMIFS('Final Project Dataset'!N:N,
         'Final Project Dataset'!D:D,
         A8)</f>
         <v>5089.7300000000005</v>
       </c>
-      <c r="C8" t="str">
+      <c r="C8" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Normal</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="str">
+      <c r="A9" s="12" t="str">
         <v>Robert Thomas</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="12">
         <f>SUMIFS('Final Project Dataset'!N:N,
         'Final Project Dataset'!D:D,
         A9)</f>
         <v>3509.8999999999996</v>
       </c>
-      <c r="C9" t="str">
+      <c r="C9" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Normal</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" t="str">
+      <c r="A10" s="12" t="str">
         <v>Karen Hill</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="12">
         <f>SUMIFS('Final Project Dataset'!N:N,
         'Final Project Dataset'!D:D,
         A10)</f>
         <v>8009.7699999999995</v>
       </c>
-      <c r="C10" t="str">
+      <c r="C10" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Normal</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" t="str">
+      <c r="A11" s="12" t="str">
         <v>Susan Green</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="12">
         <f>SUMIFS('Final Project Dataset'!N:N,
         'Final Project Dataset'!D:D,
         A11)</f>
         <v>1979.89</v>
       </c>
-      <c r="C11" t="str">
+      <c r="C11" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Normal</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" t="str">
+      <c r="A12" s="12" t="str">
         <v>Peter Richardson</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="12">
         <f>SUMIFS('Final Project Dataset'!N:N,
         'Final Project Dataset'!D:D,
         A12)</f>
         <v>5949.85</v>
       </c>
-      <c r="C12" t="str">
+      <c r="C12" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Normal</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" t="str">
+      <c r="A13" s="12" t="str">
         <v>Dennis Gray</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="12">
         <f>SUMIFS('Final Project Dataset'!N:N,
         'Final Project Dataset'!D:D,
         A13)</f>
         <v>479.91999999999996</v>
       </c>
-      <c r="C13" t="str">
+      <c r="C13" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Normal</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" t="str">
+      <c r="A14" s="12" t="str">
         <v>Michelle Rogers</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="12">
         <f>SUMIFS('Final Project Dataset'!N:N,
         'Final Project Dataset'!D:D,
         A14)</f>
         <v>4199.9399999999996</v>
       </c>
-      <c r="C14" t="str">
+      <c r="C14" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Normal</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" t="str">
+      <c r="A15" s="12" t="str">
         <v>George Adams</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="12">
         <f>SUMIFS('Final Project Dataset'!N:N,
         'Final Project Dataset'!D:D,
         A15)</f>
         <v>3779.93</v>
       </c>
-      <c r="C15" t="str">
+      <c r="C15" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Normal</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" t="str">
+      <c r="A16" s="12" t="str">
         <v>Mark Carter</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="12">
         <f>SUMIFS('Final Project Dataset'!N:N,
         'Final Project Dataset'!D:D,
         A16)</f>
         <v>15659.65</v>
       </c>
-      <c r="C16" t="str">
+      <c r="C16" s="12" t="str">
         <f t="shared" si="0"/>
         <v>High Value</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" t="str">
+      <c r="A17" s="12" t="str">
         <v>Maria Garcia</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="12">
         <f>SUMIFS('Final Project Dataset'!N:N,
         'Final Project Dataset'!D:D,
         A17)</f>
         <v>1909.93</v>
       </c>
-      <c r="C17" t="str">
+      <c r="C17" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Normal</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" t="str">
+      <c r="A18" s="12" t="str">
         <v>Virginia Sanders</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="12">
         <f>SUMIFS('Final Project Dataset'!N:N,
         'Final Project Dataset'!D:D,
         A18)</f>
         <v>4789.7900000000009</v>
       </c>
-      <c r="C18" t="str">
+      <c r="C18" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Normal</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" t="str">
+      <c r="A19" s="12" t="str">
         <v>Barbara Young</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="12">
         <f>SUMIFS('Final Project Dataset'!N:N,
         'Final Project Dataset'!D:D,
         A19)</f>
         <v>10649.8</v>
       </c>
-      <c r="C19" t="str">
+      <c r="C19" s="12" t="str">
         <f t="shared" si="0"/>
         <v>High Value</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" t="str">
+      <c r="A20" s="12" t="str">
         <v>Patricia Moore</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="12">
         <f>SUMIFS('Final Project Dataset'!N:N,
         'Final Project Dataset'!D:D,
         A20)</f>
         <v>9799.73</v>
       </c>
-      <c r="C20" t="str">
+      <c r="C20" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Normal</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" t="str">
+      <c r="A21" s="12" t="str">
         <v>Cynthia Price</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="12">
         <f>SUMIFS('Final Project Dataset'!N:N,
         'Final Project Dataset'!D:D,
         A21)</f>
         <v>3769.8300000000004</v>
       </c>
-      <c r="C21" t="str">
+      <c r="C21" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Normal</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" t="str">
+      <c r="A22" s="12" t="str">
         <v>Nancy Collins</v>
       </c>
-      <c r="B22">
+      <c r="B22" s="12">
         <f>SUMIFS('Final Project Dataset'!N:N,
         'Final Project Dataset'!D:D,
         A22)</f>
         <v>4189.7700000000004</v>
       </c>
-      <c r="C22" t="str">
+      <c r="C22" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Normal</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" t="str">
+      <c r="A23" s="12" t="str">
         <v>Linda Martin</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="12">
         <f>SUMIFS('Final Project Dataset'!N:N,
         'Final Project Dataset'!D:D,
         A23)</f>
         <v>1289.9000000000001</v>
       </c>
-      <c r="C23" t="str">
+      <c r="C23" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Normal</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" t="str">
+      <c r="A24" s="12" t="str">
         <v>Helen Roberts</v>
       </c>
-      <c r="B24">
+      <c r="B24" s="12">
         <f>SUMIFS('Final Project Dataset'!N:N,
         'Final Project Dataset'!D:D,
         A24)</f>
         <v>6459.79</v>
       </c>
-      <c r="C24" t="str">
+      <c r="C24" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Normal</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" t="str">
+      <c r="A25" s="12" t="str">
         <v>Edward Mitchell</v>
       </c>
-      <c r="B25">
+      <c r="B25" s="12">
         <f>SUMIFS('Final Project Dataset'!N:N,
         'Final Project Dataset'!D:D,
         A25)</f>
         <v>11919.769999999999</v>
       </c>
-      <c r="C25" t="str">
+      <c r="C25" s="12" t="str">
         <f t="shared" si="0"/>
         <v>High Value</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" t="str">
+      <c r="A26" s="12" t="str">
         <v>Lisa Anderson</v>
       </c>
-      <c r="B26">
+      <c r="B26" s="12">
         <f>SUMIFS('Final Project Dataset'!N:N,
         'Final Project Dataset'!D:D,
         A26)</f>
         <v>2039.8000000000002</v>
       </c>
-      <c r="C26" t="str">
+      <c r="C26" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Normal</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" t="str">
+      <c r="A27" s="12" t="str">
         <v>Emma Wilson</v>
       </c>
-      <c r="B27">
+      <c r="B27" s="12">
         <f>SUMIFS('Final Project Dataset'!N:N,
         'Final Project Dataset'!D:D,
         A27)</f>
         <v>1229.8800000000001</v>
       </c>
-      <c r="C27" t="str">
+      <c r="C27" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Normal</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" t="str">
+      <c r="A28" s="12" t="str">
         <v>Steven Turner</v>
       </c>
-      <c r="B28">
+      <c r="B28" s="12">
         <f>SUMIFS('Final Project Dataset'!N:N,
         'Final Project Dataset'!D:D,
         A28)</f>
         <v>2649.83</v>
       </c>
-      <c r="C28" t="str">
+      <c r="C28" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Normal</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" t="str">
+      <c r="A29" s="12" t="str">
         <v>Jennifer Taylor</v>
       </c>
-      <c r="B29">
+      <c r="B29" s="12">
         <f>SUMIFS('Final Project Dataset'!N:N,
         'Final Project Dataset'!D:D,
         A29)</f>
         <v>4739.8500000000004</v>
       </c>
-      <c r="C29" t="str">
+      <c r="C29" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Normal</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" t="str">
+      <c r="A30" s="12" t="str">
         <v>Harry Morgan</v>
       </c>
-      <c r="B30">
+      <c r="B30" s="12">
         <f>SUMIFS('Final Project Dataset'!N:N,
         'Final Project Dataset'!D:D,
         A30)</f>
         <v>5519.8899999999994</v>
       </c>
-      <c r="C30" t="str">
+      <c r="C30" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Normal</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" t="str">
+      <c r="A31" s="12" t="str">
         <v>Daniel King</v>
       </c>
-      <c r="B31">
+      <c r="B31" s="12">
         <f>SUMIFS('Final Project Dataset'!N:N,
         'Final Project Dataset'!D:D,
         A31)</f>
         <v>7309.7999999999993</v>
       </c>
-      <c r="C31" t="str">
+      <c r="C31" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Normal</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" t="str">
+      <c r="A32" s="12" t="str">
         <v>Sharon Butler</v>
       </c>
-      <c r="B32">
+      <c r="B32" s="12">
         <f>SUMIFS('Final Project Dataset'!N:N,
         'Final Project Dataset'!D:D,
         A32)</f>
         <v>5619.869999999999</v>
       </c>
-      <c r="C32" t="str">
+      <c r="C32" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Normal</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" t="str">
+      <c r="A33" s="12" t="str">
         <v>Sarah Davis</v>
       </c>
-      <c r="B33">
+      <c r="B33" s="12">
         <f>SUMIFS('Final Project Dataset'!N:N,
         'Final Project Dataset'!D:D,
         A33)</f>
         <v>5499.8099999999995</v>
       </c>
-      <c r="C33" t="str">
+      <c r="C33" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Normal</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" t="str">
+      <c r="A34" s="12" t="str">
         <v>Betty Campbell</v>
       </c>
-      <c r="B34">
+      <c r="B34" s="12">
         <f>SUMIFS('Final Project Dataset'!N:N,
         'Final Project Dataset'!D:D,
         A34)</f>
         <v>5649.84</v>
       </c>
-      <c r="C34" t="str">
+      <c r="C34" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Normal</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" t="str">
+      <c r="A35" s="12" t="str">
         <v>Julie Foster</v>
       </c>
-      <c r="B35">
+      <c r="B35" s="12">
         <f>SUMIFS('Final Project Dataset'!N:N,
         'Final Project Dataset'!D:D,
         A35)</f>
         <v>239.96</v>
       </c>
-      <c r="C35" t="str">
+      <c r="C35" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Normal</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" t="str">
+      <c r="A36" s="12" t="str">
         <v>Raymond Ross</v>
       </c>
-      <c r="B36">
+      <c r="B36" s="12">
         <f>SUMIFS('Final Project Dataset'!N:N,
         'Final Project Dataset'!D:D,
         A36)</f>
         <v>3669.8500000000004</v>
       </c>
-      <c r="C36" t="str">
+      <c r="C36" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Normal</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37" t="str">
+      <c r="A37" s="12" t="str">
         <v>David Martinez</v>
       </c>
-      <c r="B37">
+      <c r="B37" s="12">
         <f>SUMIFS('Final Project Dataset'!N:N,
         'Final Project Dataset'!D:D,
         A37)</f>
         <v>1809.84</v>
       </c>
-      <c r="C37" t="str">
+      <c r="C37" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Normal</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38" t="str">
+      <c r="A38" s="12" t="str">
         <v>Margaret Wright</v>
       </c>
-      <c r="B38">
+      <c r="B38" s="12">
         <f>SUMIFS('Final Project Dataset'!N:N,
         'Final Project Dataset'!D:D,
         A38)</f>
         <v>2099.88</v>
       </c>
-      <c r="C38" t="str">
+      <c r="C38" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Normal</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A39" t="str">
+      <c r="A39" s="12" t="str">
         <v>Frank Torres</v>
       </c>
-      <c r="B39">
+      <c r="B39" s="12">
         <f>SUMIFS('Final Project Dataset'!N:N,
         'Final Project Dataset'!D:D,
         A39)</f>
         <v>1479.91</v>
       </c>
-      <c r="C39" t="str">
+      <c r="C39" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Normal</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A40" t="str">
+      <c r="A40" s="12" t="str">
         <v>Gerald Murphy</v>
       </c>
-      <c r="B40">
+      <c r="B40" s="12">
         <f>SUMIFS('Final Project Dataset'!N:N,
         'Final Project Dataset'!D:D,
         A40)</f>
         <v>6379.87</v>
       </c>
-      <c r="C40" t="str">
+      <c r="C40" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Normal</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A41" t="str">
+      <c r="A41" s="12" t="str">
         <v>Elizabeth Hall</v>
       </c>
-      <c r="B41">
+      <c r="B41" s="12">
         <f>SUMIFS('Final Project Dataset'!N:N,
         'Final Project Dataset'!D:D,
         A41)</f>
         <v>3649.8599999999997</v>
       </c>
-      <c r="C41" t="str">
+      <c r="C41" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Normal</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A42" t="str">
+      <c r="A42" s="12" t="str">
         <v>Lawrence Reed</v>
       </c>
-      <c r="B42">
+      <c r="B42" s="12">
         <f>SUMIFS('Final Project Dataset'!N:N,
         'Final Project Dataset'!D:D,
         A42)</f>
         <v>6989.7699999999986</v>
       </c>
-      <c r="C42" t="str">
+      <c r="C42" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Normal</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A43" t="str">
+      <c r="A43" s="12" t="str">
         <v>Carol Evans</v>
       </c>
-      <c r="B43">
+      <c r="B43" s="12">
         <f>SUMIFS('Final Project Dataset'!N:N,
         'Final Project Dataset'!D:D,
         A43)</f>
         <v>1149.93</v>
       </c>
-      <c r="C43" t="str">
+      <c r="C43" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Normal</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A44" t="str">
+      <c r="A44" s="12" t="str">
         <v>Sandra Phillips</v>
       </c>
-      <c r="B44">
+      <c r="B44" s="12">
         <f>SUMIFS('Final Project Dataset'!N:N,
         'Final Project Dataset'!D:D,
         A44)</f>
         <v>6349.83</v>
       </c>
-      <c r="C44" t="str">
+      <c r="C44" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Normal</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A45" t="str">
+      <c r="A45" s="12" t="str">
         <v>Ruth Brooks</v>
       </c>
-      <c r="B45">
+      <c r="B45" s="12">
         <f>SUMIFS('Final Project Dataset'!N:N,
         'Final Project Dataset'!D:D,
         A45)</f>
         <v>1749.92</v>
       </c>
-      <c r="C45" t="str">
+      <c r="C45" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Normal</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A46" t="str">
+      <c r="A46" s="12" t="str">
         <v>William White</v>
       </c>
-      <c r="B46">
+      <c r="B46" s="12">
         <f>SUMIFS('Final Project Dataset'!N:N,
         'Final Project Dataset'!D:D,
         A46)</f>
         <v>4749.91</v>
       </c>
-      <c r="C46" t="str">
+      <c r="C46" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Normal</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A47" t="str">
+      <c r="A47" s="12" t="str">
         <v>Richard Lee</v>
       </c>
-      <c r="B47">
+      <c r="B47" s="12">
         <f>SUMIFS('Final Project Dataset'!N:N,
         'Final Project Dataset'!D:D,
         A47)</f>
         <v>739.93000000000006</v>
       </c>
-      <c r="C47" t="str">
+      <c r="C47" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Normal</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A48" t="str">
+      <c r="A48" s="12" t="str">
         <v>Douglas Watson</v>
       </c>
-      <c r="B48">
+      <c r="B48" s="12">
         <f>SUMIFS('Final Project Dataset'!N:N,
         'Final Project Dataset'!D:D,
         A48)</f>
         <v>4829.8899999999994</v>
       </c>
-      <c r="C48" t="str">
+      <c r="C48" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Normal</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A49" t="str">
+      <c r="A49" s="12" t="str">
         <v>James Johnson</v>
       </c>
-      <c r="B49">
+      <c r="B49" s="12">
         <f>SUMIFS('Final Project Dataset'!N:N,
         'Final Project Dataset'!D:D,
         A49)</f>
         <v>179.97</v>
       </c>
-      <c r="C49" t="str">
+      <c r="C49" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Normal</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A50" t="str">
+      <c r="A50" s="12" t="str">
         <v>Arthur Edwards</v>
       </c>
-      <c r="B50">
+      <c r="B50" s="12">
         <f>SUMIFS('Final Project Dataset'!N:N,
         'Final Project Dataset'!D:D,
         A50)</f>
         <v>1559.94</v>
       </c>
-      <c r="C50" t="str">
+      <c r="C50" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Normal</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A51" t="str">
+      <c r="A51" s="12" t="str">
         <v>John Smith</v>
       </c>
-      <c r="B51">
+      <c r="B51" s="12">
         <f>SUMIFS('Final Project Dataset'!N:N,
         'Final Project Dataset'!D:D,
         A51)</f>
         <v>599.96</v>
       </c>
-      <c r="C51" t="str">
+      <c r="C51" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Normal</v>
       </c>
@@ -63836,7 +63778,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36415BE1-4D6D-4B4C-AFA7-D47F6C54350E}">
-  <dimension ref="A1:O132"/>
+  <dimension ref="A1:O77"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.6640625" customWidth="1"/>
@@ -63896,117 +63838,117 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="B2" t="str" cm="1">
-        <f t="array" ref="B2:O132">_xlfn._xlws.FILTER('Final Project Dataset'!A:N,'Final Project Dataset'!G:G=Filter!A2,"-")</f>
-        <v>TRX0155</v>
+        <f t="array" ref="B2:O77">_xlfn._xlws.FILTER('Final Project Dataset'!A:N,'Final Project Dataset'!G:G=Filter!A2,"-")</f>
+        <v>TRX0212</v>
       </c>
       <c r="C2" s="13">
-        <v>45393</v>
+        <v>45400</v>
       </c>
       <c r="D2" t="str">
-        <v>CUST01</v>
+        <v>CUST05</v>
       </c>
       <c r="E2" t="str">
-        <v>Paul Baker</v>
+        <v>Michael Brown</v>
       </c>
       <c r="F2" t="str">
-        <v>P009</v>
+        <v>P008</v>
       </c>
       <c r="G2" t="str">
-        <v>Monitor</v>
+        <v>Bookshelf</v>
       </c>
       <c r="H2" t="str">
-        <v>Electronics</v>
+        <v>Furniture</v>
       </c>
       <c r="I2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J2">
-        <v>249.99</v>
+        <v>149.99</v>
       </c>
       <c r="K2" t="str">
-        <v>Cash</v>
+        <v>Credit Card</v>
       </c>
       <c r="L2" t="str">
-        <v>Central</v>
+        <v>North</v>
       </c>
       <c r="M2" t="str">
-        <v>Basic</v>
+        <v>Premium</v>
       </c>
       <c r="N2" s="13">
-        <v>44425</v>
+        <v>45295</v>
       </c>
       <c r="O2">
-        <v>749.97</v>
+        <v>749.95</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B3" t="str">
-        <v>TRX0023</v>
+        <v>TRX0138</v>
       </c>
       <c r="C3" s="13">
-        <v>45396</v>
+        <v>45408</v>
       </c>
       <c r="D3" t="str">
-        <v>CUST02</v>
+        <v>CUST11</v>
       </c>
       <c r="E3" t="str">
-        <v>Joseph Jackson</v>
+        <v>Susan Green</v>
       </c>
       <c r="F3" t="str">
-        <v>P009</v>
+        <v>P008</v>
       </c>
       <c r="G3" t="str">
-        <v>Monitor</v>
+        <v>Bookshelf</v>
       </c>
       <c r="H3" t="str">
-        <v>Electronics</v>
+        <v>Furniture</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>249.99</v>
+        <v>149.99</v>
       </c>
       <c r="K3" t="str">
         <v>Credit Card</v>
       </c>
       <c r="L3" t="str">
-        <v>Central</v>
+        <v>West</v>
       </c>
       <c r="M3" t="str">
-        <v>Premium</v>
+        <v>Standard</v>
       </c>
       <c r="N3" s="13">
-        <v>44575</v>
+        <v>45103</v>
       </c>
       <c r="O3">
-        <v>749.97</v>
+        <v>149.99</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B4" t="str">
-        <v>TRX0193</v>
+        <v>TRX0209</v>
       </c>
       <c r="C4" s="13">
-        <v>45403</v>
+        <v>45408</v>
       </c>
       <c r="D4" t="str">
-        <v>CUST07</v>
+        <v>CUST12</v>
       </c>
       <c r="E4" t="str">
-        <v>Dorothy Nelson</v>
+        <v>Kathleen Bennett</v>
       </c>
       <c r="F4" t="str">
-        <v>P003</v>
+        <v>P008</v>
       </c>
       <c r="G4" t="str">
-        <v>Headphones</v>
+        <v>Bookshelf</v>
       </c>
       <c r="H4" t="str">
-        <v>Electronics</v>
+        <v>Furniture</v>
       </c>
       <c r="I4">
         <v>5</v>
@@ -64015,16 +63957,16 @@
         <v>149.99</v>
       </c>
       <c r="K4" t="str">
-        <v>Credit Card</v>
+        <v>Debit Card</v>
       </c>
       <c r="L4" t="str">
-        <v>Central</v>
+        <v>North</v>
       </c>
       <c r="M4" t="str">
-        <v>Standard</v>
+        <v>Basic</v>
       </c>
       <c r="N4" s="13">
-        <v>44418</v>
+        <v>44830</v>
       </c>
       <c r="O4">
         <v>749.95</v>
@@ -64032,647 +63974,647 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B5" t="str">
-        <v>TRX0135</v>
+        <v>TRX0246</v>
       </c>
       <c r="C5" s="13">
-        <v>45405</v>
+        <v>45408</v>
       </c>
       <c r="D5" t="str">
-        <v>CUST09</v>
+        <v>CUST13</v>
       </c>
       <c r="E5" t="str">
-        <v>Robert Thomas</v>
+        <v>Peter Richardson</v>
       </c>
       <c r="F5" t="str">
-        <v>P001</v>
+        <v>P008</v>
       </c>
       <c r="G5" t="str">
-        <v>Laptop</v>
+        <v>Bookshelf</v>
       </c>
       <c r="H5" t="str">
-        <v>Electronics</v>
+        <v>Furniture</v>
       </c>
       <c r="I5">
         <v>3</v>
       </c>
       <c r="J5">
-        <v>899.99</v>
+        <v>149.99</v>
       </c>
       <c r="K5" t="str">
-        <v>PayPal</v>
+        <v>Cash</v>
       </c>
       <c r="L5" t="str">
-        <v>East</v>
+        <v>North</v>
       </c>
       <c r="M5" t="str">
-        <v>Standard</v>
+        <v>Premium</v>
       </c>
       <c r="N5" s="13">
-        <v>45299</v>
+        <v>44806</v>
       </c>
       <c r="O5">
-        <v>2699.97</v>
+        <v>449.97</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B6" t="str">
-        <v>TRX0191</v>
+        <v>TRX0049</v>
       </c>
       <c r="C6" s="13">
-        <v>45409</v>
+        <v>45410</v>
       </c>
       <c r="D6" t="str">
-        <v>CUST15</v>
+        <v>CUST17</v>
       </c>
       <c r="E6" t="str">
-        <v>Michelle Rogers</v>
+        <v>Mark Carter</v>
       </c>
       <c r="F6" t="str">
-        <v>P002</v>
+        <v>P008</v>
       </c>
       <c r="G6" t="str">
-        <v>Smartphone</v>
+        <v>Bookshelf</v>
       </c>
       <c r="H6" t="str">
-        <v>Electronics</v>
+        <v>Furniture</v>
       </c>
       <c r="I6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J6">
-        <v>699.99</v>
+        <v>149.99</v>
       </c>
       <c r="K6" t="str">
-        <v>Credit Card</v>
+        <v>Debit Card</v>
       </c>
       <c r="L6" t="str">
-        <v>West</v>
+        <v>North</v>
       </c>
       <c r="M6" t="str">
-        <v>Basic</v>
+        <v>Premium</v>
       </c>
       <c r="N6" s="13">
-        <v>44577</v>
+        <v>45374</v>
       </c>
       <c r="O6">
-        <v>2099.9699999999998</v>
+        <v>599.96</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B7" t="str">
-        <v>TRX0230</v>
+        <v>TRX0242</v>
       </c>
       <c r="C7" s="13">
-        <v>45409</v>
+        <v>45416</v>
       </c>
       <c r="D7" t="str">
-        <v>CUST16</v>
+        <v>CUST24</v>
       </c>
       <c r="E7" t="str">
-        <v>George Adams</v>
+        <v>Mark Carter</v>
       </c>
       <c r="F7" t="str">
-        <v>P001</v>
+        <v>P007</v>
       </c>
       <c r="G7" t="str">
-        <v>Laptop</v>
+        <v>Desk</v>
       </c>
       <c r="H7" t="str">
-        <v>Electronics</v>
+        <v>Furniture</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J7">
-        <v>899.99</v>
+        <v>299.99</v>
       </c>
       <c r="K7" t="str">
-        <v>Debit Card</v>
+        <v>Cash</v>
       </c>
       <c r="L7" t="str">
-        <v>North</v>
+        <v>West</v>
       </c>
       <c r="M7" t="str">
-        <v>Standard</v>
+        <v>Premium</v>
       </c>
       <c r="N7" s="13">
-        <v>44920</v>
+        <v>44716</v>
       </c>
       <c r="O7">
-        <v>899.99</v>
+        <v>1199.96</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B8" t="str">
-        <v>TRX0134</v>
+        <v>TRX0040</v>
       </c>
       <c r="C8" s="13">
-        <v>45410</v>
+        <v>45424</v>
       </c>
       <c r="D8" t="str">
-        <v>CUST18</v>
+        <v>CUST26</v>
       </c>
       <c r="E8" t="str">
-        <v>Maria Garcia</v>
+        <v>Susan Green</v>
       </c>
       <c r="F8" t="str">
-        <v>P002</v>
+        <v>P007</v>
       </c>
       <c r="G8" t="str">
-        <v>Smartphone</v>
+        <v>Desk</v>
       </c>
       <c r="H8" t="str">
-        <v>Electronics</v>
+        <v>Furniture</v>
       </c>
       <c r="I8">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J8">
-        <v>699.99</v>
+        <v>299.99</v>
       </c>
       <c r="K8" t="str">
-        <v>Cash</v>
+        <v>PayPal</v>
       </c>
       <c r="L8" t="str">
-        <v>North</v>
+        <v>East</v>
       </c>
       <c r="M8" t="str">
         <v>Basic</v>
       </c>
       <c r="N8" s="13">
-        <v>44781</v>
+        <v>45168</v>
       </c>
       <c r="O8">
-        <v>1399.98</v>
+        <v>1499.95</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B9" t="str">
-        <v>TRX0122</v>
+        <v>TRX0029</v>
       </c>
       <c r="C9" s="13">
-        <v>45410</v>
+        <v>45427</v>
       </c>
       <c r="D9" t="str">
-        <v>CUST19</v>
+        <v>CUST31</v>
       </c>
       <c r="E9" t="str">
-        <v>Mark Carter</v>
+        <v>Charles Allen</v>
       </c>
       <c r="F9" t="str">
-        <v>P001</v>
+        <v>P006</v>
       </c>
       <c r="G9" t="str">
-        <v>Laptop</v>
+        <v>Office Chair</v>
       </c>
       <c r="H9" t="str">
-        <v>Electronics</v>
+        <v>Furniture</v>
       </c>
       <c r="I9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J9">
-        <v>899.99</v>
+        <v>199.99</v>
       </c>
       <c r="K9" t="str">
-        <v>Credit Card</v>
+        <v>Cash</v>
       </c>
       <c r="L9" t="str">
-        <v>West</v>
+        <v>South</v>
       </c>
       <c r="M9" t="str">
         <v>Standard</v>
       </c>
       <c r="N9" s="13">
-        <v>45327</v>
+        <v>44412</v>
       </c>
       <c r="O9">
-        <v>3599.96</v>
+        <v>999.95</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B10" t="str">
-        <v>TRX0222</v>
+        <v>TRX0194</v>
       </c>
       <c r="C10" s="13">
-        <v>45410</v>
+        <v>45428</v>
       </c>
       <c r="D10" t="str">
-        <v>CUST20</v>
+        <v>CUST32</v>
       </c>
       <c r="E10" t="str">
-        <v>Virginia Sanders</v>
+        <v>Lisa Anderson</v>
       </c>
       <c r="F10" t="str">
-        <v>P009</v>
+        <v>P008</v>
       </c>
       <c r="G10" t="str">
-        <v>Monitor</v>
+        <v>Bookshelf</v>
       </c>
       <c r="H10" t="str">
-        <v>Electronics</v>
+        <v>Furniture</v>
       </c>
       <c r="I10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J10">
-        <v>249.99</v>
+        <v>149.99</v>
       </c>
       <c r="K10" t="str">
         <v>Credit Card</v>
       </c>
       <c r="L10" t="str">
-        <v>North</v>
+        <v>West</v>
       </c>
       <c r="M10" t="str">
-        <v>Premium</v>
+        <v>Basic</v>
       </c>
       <c r="N10" s="13">
-        <v>45224</v>
+        <v>44823</v>
       </c>
       <c r="O10">
-        <v>749.97</v>
+        <v>299.98</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B11" t="str">
-        <v>TRX0231</v>
+        <v>TRX0130</v>
       </c>
       <c r="C11" s="13">
-        <v>45412</v>
+        <v>45430</v>
       </c>
       <c r="D11" t="str">
-        <v>CUST21</v>
+        <v>CUST33</v>
       </c>
       <c r="E11" t="str">
-        <v>Barbara Young</v>
+        <v>Emma Wilson</v>
       </c>
       <c r="F11" t="str">
-        <v>P002</v>
+        <v>P008</v>
       </c>
       <c r="G11" t="str">
-        <v>Smartphone</v>
+        <v>Bookshelf</v>
       </c>
       <c r="H11" t="str">
-        <v>Electronics</v>
+        <v>Furniture</v>
       </c>
       <c r="I11">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J11">
-        <v>699.99</v>
+        <v>149.99</v>
       </c>
       <c r="K11" t="str">
-        <v>Cash</v>
+        <v>Credit Card</v>
       </c>
       <c r="L11" t="str">
         <v>West</v>
       </c>
       <c r="M11" t="str">
-        <v>Basic</v>
+        <v>Premium</v>
       </c>
       <c r="N11" s="13">
-        <v>45167</v>
+        <v>45068</v>
       </c>
       <c r="O11">
-        <v>3499.95</v>
+        <v>449.97</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B12" t="str">
-        <v>TRX0239</v>
+        <v>TRX0232</v>
       </c>
       <c r="C12" s="13">
-        <v>45413</v>
+        <v>45434</v>
       </c>
       <c r="D12" t="str">
-        <v>CUST22</v>
+        <v>CUST35</v>
       </c>
       <c r="E12" t="str">
         <v>Patricia Moore</v>
       </c>
       <c r="F12" t="str">
-        <v>P002</v>
+        <v>P007</v>
       </c>
       <c r="G12" t="str">
-        <v>Smartphone</v>
+        <v>Desk</v>
       </c>
       <c r="H12" t="str">
-        <v>Electronics</v>
+        <v>Furniture</v>
       </c>
       <c r="I12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J12">
-        <v>699.99</v>
+        <v>299.99</v>
       </c>
       <c r="K12" t="str">
-        <v>Cash</v>
+        <v>Credit Card</v>
       </c>
       <c r="L12" t="str">
         <v>East</v>
       </c>
       <c r="M12" t="str">
-        <v>Standard</v>
+        <v>Basic</v>
       </c>
       <c r="N12" s="13">
-        <v>44409</v>
+        <v>44824</v>
       </c>
       <c r="O12">
-        <v>2799.96</v>
+        <v>899.97</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B13" t="str">
-        <v>TRX0204</v>
+        <v>TRX0245</v>
       </c>
       <c r="C13" s="13">
-        <v>45415</v>
+        <v>45438</v>
       </c>
       <c r="D13" t="str">
-        <v>CUST23</v>
+        <v>CUST37</v>
       </c>
       <c r="E13" t="str">
-        <v>Cynthia Price</v>
+        <v>Steven Turner</v>
       </c>
       <c r="F13" t="str">
-        <v>P009</v>
+        <v>P006</v>
       </c>
       <c r="G13" t="str">
-        <v>Monitor</v>
+        <v>Office Chair</v>
       </c>
       <c r="H13" t="str">
-        <v>Electronics</v>
+        <v>Furniture</v>
       </c>
       <c r="I13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J13">
-        <v>249.99</v>
+        <v>199.99</v>
       </c>
       <c r="K13" t="str">
-        <v>PayPal</v>
+        <v>Credit Card</v>
       </c>
       <c r="L13" t="str">
         <v>North</v>
       </c>
       <c r="M13" t="str">
-        <v>Standard</v>
+        <v>Premium</v>
       </c>
       <c r="N13" s="13">
-        <v>44468</v>
+        <v>45292</v>
       </c>
       <c r="O13">
-        <v>999.96</v>
+        <v>599.97</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B14" t="str">
-        <v>TRX0071</v>
+        <v>TRX0220</v>
       </c>
       <c r="C14" s="13">
-        <v>45422</v>
+        <v>45450</v>
       </c>
       <c r="D14" t="str">
-        <v>CUST25</v>
+        <v>CUST46</v>
       </c>
       <c r="E14" t="str">
-        <v>Nancy Collins</v>
+        <v>Michael Brown</v>
       </c>
       <c r="F14" t="str">
-        <v>P009</v>
+        <v>P008</v>
       </c>
       <c r="G14" t="str">
-        <v>Monitor</v>
+        <v>Bookshelf</v>
       </c>
       <c r="H14" t="str">
-        <v>Electronics</v>
+        <v>Furniture</v>
       </c>
       <c r="I14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J14">
-        <v>249.99</v>
+        <v>149.99</v>
       </c>
       <c r="K14" t="str">
-        <v>Credit Card</v>
+        <v>Cash</v>
       </c>
       <c r="L14" t="str">
-        <v>West</v>
+        <v>East</v>
       </c>
       <c r="M14" t="str">
-        <v>Standard</v>
+        <v>Premium</v>
       </c>
       <c r="N14" s="13">
-        <v>44525</v>
+        <v>44645</v>
       </c>
       <c r="O14">
-        <v>1249.95</v>
+        <v>299.98</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B15" t="str">
-        <v>TRX0004</v>
+        <v>TRX0150</v>
       </c>
       <c r="C15" s="13">
-        <v>45424</v>
+        <v>45460</v>
       </c>
       <c r="D15" t="str">
-        <v>CUST28</v>
+        <v>CUST53</v>
       </c>
       <c r="E15" t="str">
-        <v>Patricia Moore</v>
+        <v>Jennifer Taylor</v>
       </c>
       <c r="F15" t="str">
-        <v>P010</v>
+        <v>P007</v>
       </c>
       <c r="G15" t="str">
-        <v>Keyboard</v>
+        <v>Desk</v>
       </c>
       <c r="H15" t="str">
-        <v>Electronics</v>
+        <v>Furniture</v>
       </c>
       <c r="I15">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J15">
-        <v>89.99</v>
+        <v>299.99</v>
       </c>
       <c r="K15" t="str">
-        <v>Cash</v>
+        <v>Debit Card</v>
       </c>
       <c r="L15" t="str">
-        <v>North</v>
+        <v>East</v>
       </c>
       <c r="M15" t="str">
-        <v>Premium</v>
+        <v>Standard</v>
       </c>
       <c r="N15" s="13">
-        <v>44919</v>
+        <v>45253</v>
       </c>
       <c r="O15">
-        <v>449.95</v>
+        <v>599.98</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B16" t="str">
-        <v>TRX0041</v>
+        <v>TRX0127</v>
       </c>
       <c r="C16" s="13">
-        <v>45432</v>
+        <v>45472</v>
       </c>
       <c r="D16" t="str">
-        <v>CUST34</v>
+        <v>CUST59</v>
       </c>
       <c r="E16" t="str">
-        <v>Kevin Scott</v>
+        <v>Helen Roberts</v>
       </c>
       <c r="F16" t="str">
-        <v>P001</v>
+        <v>P008</v>
       </c>
       <c r="G16" t="str">
-        <v>Laptop</v>
+        <v>Bookshelf</v>
       </c>
       <c r="H16" t="str">
-        <v>Electronics</v>
+        <v>Furniture</v>
       </c>
       <c r="I16">
         <v>1</v>
       </c>
       <c r="J16">
-        <v>899.99</v>
+        <v>149.99</v>
       </c>
       <c r="K16" t="str">
-        <v>Credit Card</v>
+        <v>PayPal</v>
       </c>
       <c r="L16" t="str">
-        <v>West</v>
+        <v>East</v>
       </c>
       <c r="M16" t="str">
-        <v>Premium</v>
+        <v>Basic</v>
       </c>
       <c r="N16" s="13">
-        <v>44578</v>
+        <v>44851</v>
       </c>
       <c r="O16">
-        <v>899.99</v>
+        <v>149.99</v>
       </c>
     </row>
     <row r="17" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B17" t="str">
-        <v>TRX0015</v>
+        <v>TRX0086</v>
       </c>
       <c r="C17" s="13">
-        <v>45440</v>
+        <v>45481</v>
       </c>
       <c r="D17" t="str">
-        <v>CUST38</v>
+        <v>CUST64</v>
       </c>
       <c r="E17" t="str">
-        <v>Jennifer Taylor</v>
+        <v>Margaret Wright</v>
       </c>
       <c r="F17" t="str">
-        <v>P002</v>
+        <v>P008</v>
       </c>
       <c r="G17" t="str">
-        <v>Smartphone</v>
+        <v>Bookshelf</v>
       </c>
       <c r="H17" t="str">
-        <v>Electronics</v>
+        <v>Furniture</v>
       </c>
       <c r="I17">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J17">
-        <v>699.99</v>
+        <v>149.99</v>
       </c>
       <c r="K17" t="str">
         <v>PayPal</v>
       </c>
       <c r="L17" t="str">
-        <v>West</v>
+        <v>North</v>
       </c>
       <c r="M17" t="str">
-        <v>Standard</v>
+        <v>Basic</v>
       </c>
       <c r="N17" s="13">
-        <v>44407</v>
+        <v>44421</v>
       </c>
       <c r="O17">
-        <v>3499.95</v>
+        <v>149.99</v>
       </c>
     </row>
     <row r="18" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B18" t="str">
-        <v>TRX0202</v>
+        <v>TRX0141</v>
       </c>
       <c r="C18" s="13">
-        <v>45441</v>
+        <v>45484</v>
       </c>
       <c r="D18" t="str">
-        <v>CUST39</v>
+        <v>CUST69</v>
       </c>
       <c r="E18" t="str">
-        <v>Harry Morgan</v>
+        <v>Frank Torres</v>
       </c>
       <c r="F18" t="str">
-        <v>P010</v>
+        <v>P007</v>
       </c>
       <c r="G18" t="str">
-        <v>Keyboard</v>
+        <v>Desk</v>
       </c>
       <c r="H18" t="str">
-        <v>Electronics</v>
+        <v>Furniture</v>
       </c>
       <c r="I18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J18">
-        <v>89.99</v>
+        <v>299.99</v>
       </c>
       <c r="K18" t="str">
-        <v>PayPal</v>
+        <v>Credit Card</v>
       </c>
       <c r="L18" t="str">
-        <v>Central</v>
+        <v>North</v>
       </c>
       <c r="M18" t="str">
         <v>Premium</v>
       </c>
       <c r="N18" s="13">
-        <v>45120</v>
+        <v>44891</v>
       </c>
       <c r="O18">
-        <v>269.97000000000003</v>
+        <v>299.99</v>
       </c>
     </row>
     <row r="19" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B19" t="str">
-        <v>TRX0117</v>
+        <v>TRX0097</v>
       </c>
       <c r="C19" s="13">
-        <v>45444</v>
+        <v>45487</v>
       </c>
       <c r="D19" t="str">
-        <v>CUST42</v>
+        <v>CUST70</v>
       </c>
       <c r="E19" t="str">
-        <v>Charles Allen</v>
+        <v>Frank Torres</v>
       </c>
       <c r="F19" t="str">
-        <v>P010</v>
+        <v>P006</v>
       </c>
       <c r="G19" t="str">
-        <v>Keyboard</v>
+        <v>Office Chair</v>
       </c>
       <c r="H19" t="str">
-        <v>Electronics</v>
+        <v>Furniture</v>
       </c>
       <c r="I19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J19">
-        <v>89.99</v>
+        <v>199.99</v>
       </c>
       <c r="K19" t="str">
         <v>Cash</v>
@@ -64684,171 +64626,171 @@
         <v>Basic</v>
       </c>
       <c r="N19" s="13">
-        <v>45141</v>
+        <v>44541</v>
       </c>
       <c r="O19">
-        <v>89.99</v>
+        <v>399.98</v>
       </c>
     </row>
     <row r="20" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B20" t="str">
-        <v>TRX0208</v>
+        <v>TRX0216</v>
       </c>
       <c r="C20" s="13">
-        <v>45446</v>
+        <v>45490</v>
       </c>
       <c r="D20" t="str">
-        <v>CUST43</v>
+        <v>CUST72</v>
       </c>
       <c r="E20" t="str">
-        <v>Sarah Davis</v>
+        <v>Peter Richardson</v>
       </c>
       <c r="F20" t="str">
-        <v>P010</v>
+        <v>P008</v>
       </c>
       <c r="G20" t="str">
-        <v>Keyboard</v>
+        <v>Bookshelf</v>
       </c>
       <c r="H20" t="str">
-        <v>Electronics</v>
+        <v>Furniture</v>
       </c>
       <c r="I20">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J20">
-        <v>89.99</v>
+        <v>149.99</v>
       </c>
       <c r="K20" t="str">
-        <v>Credit Card</v>
+        <v>Cash</v>
       </c>
       <c r="L20" t="str">
-        <v>East</v>
+        <v>Central</v>
       </c>
       <c r="M20" t="str">
-        <v>Standard</v>
+        <v>Premium</v>
       </c>
       <c r="N20" s="13">
-        <v>44587</v>
+        <v>45199</v>
       </c>
       <c r="O20">
-        <v>449.95</v>
+        <v>449.97</v>
       </c>
     </row>
     <row r="21" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B21" t="str">
-        <v>TRX0234</v>
+        <v>TRX0131</v>
       </c>
       <c r="C21" s="13">
-        <v>45449</v>
+        <v>45491</v>
       </c>
       <c r="D21" t="str">
-        <v>CUST44</v>
+        <v>CUST73</v>
       </c>
       <c r="E21" t="str">
-        <v>Joseph Jackson</v>
+        <v>Karen Hill</v>
       </c>
       <c r="F21" t="str">
-        <v>P009</v>
+        <v>P006</v>
       </c>
       <c r="G21" t="str">
-        <v>Monitor</v>
+        <v>Office Chair</v>
       </c>
       <c r="H21" t="str">
-        <v>Electronics</v>
+        <v>Furniture</v>
       </c>
       <c r="I21">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J21">
-        <v>249.99</v>
+        <v>199.99</v>
       </c>
       <c r="K21" t="str">
-        <v>Credit Card</v>
+        <v>Cash</v>
       </c>
       <c r="L21" t="str">
-        <v>East</v>
+        <v>North</v>
       </c>
       <c r="M21" t="str">
-        <v>Standard</v>
+        <v>Premium</v>
       </c>
       <c r="N21" s="13">
-        <v>44707</v>
+        <v>45254</v>
       </c>
       <c r="O21">
-        <v>1249.95</v>
+        <v>599.97</v>
       </c>
     </row>
     <row r="22" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B22" t="str">
-        <v>TRX0121</v>
+        <v>TRX0228</v>
       </c>
       <c r="C22" s="13">
-        <v>45449</v>
+        <v>45500</v>
       </c>
       <c r="D22" t="str">
-        <v>CUST45</v>
+        <v>CUST79</v>
       </c>
       <c r="E22" t="str">
-        <v>Betty Campbell</v>
+        <v>Daniel King</v>
       </c>
       <c r="F22" t="str">
-        <v>P010</v>
+        <v>P007</v>
       </c>
       <c r="G22" t="str">
-        <v>Keyboard</v>
+        <v>Desk</v>
       </c>
       <c r="H22" t="str">
-        <v>Electronics</v>
+        <v>Furniture</v>
       </c>
       <c r="I22">
         <v>1</v>
       </c>
       <c r="J22">
-        <v>89.99</v>
+        <v>299.99</v>
       </c>
       <c r="K22" t="str">
-        <v>Credit Card</v>
+        <v>Cash</v>
       </c>
       <c r="L22" t="str">
         <v>South</v>
       </c>
       <c r="M22" t="str">
-        <v>Standard</v>
+        <v>Basic</v>
       </c>
       <c r="N22" s="13">
-        <v>44582</v>
+        <v>44982</v>
       </c>
       <c r="O22">
-        <v>89.99</v>
+        <v>299.99</v>
       </c>
     </row>
     <row r="23" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B23" t="str">
-        <v>TRX0088</v>
+        <v>TRX0002</v>
       </c>
       <c r="C23" s="13">
-        <v>45456</v>
+        <v>45501</v>
       </c>
       <c r="D23" t="str">
-        <v>CUST48</v>
+        <v>CUST81</v>
       </c>
       <c r="E23" t="str">
-        <v>Lisa Anderson</v>
+        <v>Daniel King</v>
       </c>
       <c r="F23" t="str">
-        <v>P010</v>
+        <v>P007</v>
       </c>
       <c r="G23" t="str">
-        <v>Keyboard</v>
+        <v>Desk</v>
       </c>
       <c r="H23" t="str">
-        <v>Electronics</v>
+        <v>Furniture</v>
       </c>
       <c r="I23">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J23">
-        <v>89.99</v>
+        <v>299.99</v>
       </c>
       <c r="K23" t="str">
         <v>Cash</v>
@@ -64857,617 +64799,617 @@
         <v>Central</v>
       </c>
       <c r="M23" t="str">
-        <v>Premium</v>
+        <v>Basic</v>
       </c>
       <c r="N23" s="13">
-        <v>44579</v>
+        <v>44732</v>
       </c>
       <c r="O23">
-        <v>449.95</v>
+        <v>899.97</v>
       </c>
     </row>
     <row r="24" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B24" t="str">
-        <v>TRX0115</v>
+        <v>TRX0065</v>
       </c>
       <c r="C24" s="13">
-        <v>45459</v>
+        <v>45509</v>
       </c>
       <c r="D24" t="str">
-        <v>CUST49</v>
+        <v>CUST84</v>
       </c>
       <c r="E24" t="str">
-        <v>Patricia Moore</v>
+        <v>Elizabeth Hall</v>
       </c>
       <c r="F24" t="str">
-        <v>P010</v>
+        <v>P008</v>
       </c>
       <c r="G24" t="str">
-        <v>Keyboard</v>
+        <v>Bookshelf</v>
       </c>
       <c r="H24" t="str">
-        <v>Electronics</v>
+        <v>Furniture</v>
       </c>
       <c r="I24">
         <v>2</v>
       </c>
       <c r="J24">
-        <v>89.99</v>
+        <v>149.99</v>
       </c>
       <c r="K24" t="str">
         <v>Credit Card</v>
       </c>
       <c r="L24" t="str">
-        <v>South</v>
+        <v>West</v>
       </c>
       <c r="M24" t="str">
-        <v>Premium</v>
+        <v>Basic</v>
       </c>
       <c r="N24" s="13">
-        <v>44471</v>
+        <v>44542</v>
       </c>
       <c r="O24">
-        <v>179.98</v>
+        <v>299.98</v>
       </c>
     </row>
     <row r="25" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B25" t="str">
-        <v>TRX0154</v>
+        <v>TRX0176</v>
       </c>
       <c r="C25" s="13">
-        <v>45459</v>
+        <v>45510</v>
       </c>
       <c r="D25" t="str">
-        <v>CUST50</v>
+        <v>CUST85</v>
       </c>
       <c r="E25" t="str">
-        <v>Paul Baker</v>
+        <v>Cynthia Price</v>
       </c>
       <c r="F25" t="str">
-        <v>P001</v>
+        <v>P008</v>
       </c>
       <c r="G25" t="str">
-        <v>Laptop</v>
+        <v>Bookshelf</v>
       </c>
       <c r="H25" t="str">
-        <v>Electronics</v>
+        <v>Furniture</v>
       </c>
       <c r="I25">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J25">
-        <v>899.99</v>
+        <v>149.99</v>
       </c>
       <c r="K25" t="str">
-        <v>Credit Card</v>
+        <v>Debit Card</v>
       </c>
       <c r="L25" t="str">
-        <v>South</v>
+        <v>East</v>
       </c>
       <c r="M25" t="str">
         <v>Standard</v>
       </c>
       <c r="N25" s="13">
-        <v>44974</v>
+        <v>44667</v>
       </c>
       <c r="O25">
-        <v>4499.95</v>
+        <v>299.98</v>
       </c>
     </row>
     <row r="26" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B26" t="str">
-        <v>TRX0044</v>
+        <v>TRX0205</v>
       </c>
       <c r="C26" s="13">
-        <v>45459</v>
+        <v>45515</v>
       </c>
       <c r="D26" t="str">
-        <v>CUST51</v>
+        <v>CUST87</v>
       </c>
       <c r="E26" t="str">
-        <v>Edward Mitchell</v>
+        <v>Mark Carter</v>
       </c>
       <c r="F26" t="str">
-        <v>P001</v>
+        <v>P007</v>
       </c>
       <c r="G26" t="str">
-        <v>Laptop</v>
+        <v>Desk</v>
       </c>
       <c r="H26" t="str">
-        <v>Electronics</v>
+        <v>Furniture</v>
       </c>
       <c r="I26">
         <v>5</v>
       </c>
       <c r="J26">
-        <v>899.99</v>
+        <v>299.99</v>
       </c>
       <c r="K26" t="str">
-        <v>PayPal</v>
+        <v>Credit Card</v>
       </c>
       <c r="L26" t="str">
-        <v>East</v>
+        <v>North</v>
       </c>
       <c r="M26" t="str">
-        <v>Premium</v>
+        <v>Basic</v>
       </c>
       <c r="N26" s="13">
-        <v>45278</v>
+        <v>44965</v>
       </c>
       <c r="O26">
-        <v>4499.95</v>
+        <v>1499.95</v>
       </c>
     </row>
     <row r="27" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B27" t="str">
-        <v>TRX0025</v>
+        <v>TRX0247</v>
       </c>
       <c r="C27" s="13">
-        <v>45468</v>
+        <v>45517</v>
       </c>
       <c r="D27" t="str">
-        <v>CUST54</v>
+        <v>CUST91</v>
       </c>
       <c r="E27" t="str">
-        <v>Raymond Ross</v>
+        <v>Kathleen Bennett</v>
       </c>
       <c r="F27" t="str">
-        <v>P010</v>
+        <v>P006</v>
       </c>
       <c r="G27" t="str">
-        <v>Keyboard</v>
+        <v>Office Chair</v>
       </c>
       <c r="H27" t="str">
-        <v>Electronics</v>
+        <v>Furniture</v>
       </c>
       <c r="I27">
         <v>4</v>
       </c>
       <c r="J27">
-        <v>89.99</v>
+        <v>199.99</v>
       </c>
       <c r="K27" t="str">
-        <v>Debit Card</v>
+        <v>Cash</v>
       </c>
       <c r="L27" t="str">
-        <v>South</v>
+        <v>North</v>
       </c>
       <c r="M27" t="str">
-        <v>Basic</v>
+        <v>Standard</v>
       </c>
       <c r="N27" s="13">
-        <v>45281</v>
+        <v>44458</v>
       </c>
       <c r="O27">
-        <v>359.96</v>
+        <v>799.96</v>
       </c>
     </row>
     <row r="28" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B28" t="str">
-        <v>TRX0007</v>
+        <v>TRX0027</v>
       </c>
       <c r="C28" s="13">
-        <v>45469</v>
+        <v>45519</v>
       </c>
       <c r="D28" t="str">
-        <v>CUST56</v>
+        <v>CUST92</v>
       </c>
       <c r="E28" t="str">
-        <v>Robert Thomas</v>
+        <v>Betty Campbell</v>
       </c>
       <c r="F28" t="str">
-        <v>P010</v>
+        <v>P006</v>
       </c>
       <c r="G28" t="str">
-        <v>Keyboard</v>
+        <v>Office Chair</v>
       </c>
       <c r="H28" t="str">
-        <v>Electronics</v>
+        <v>Furniture</v>
       </c>
       <c r="I28">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J28">
-        <v>89.99</v>
+        <v>199.99</v>
       </c>
       <c r="K28" t="str">
         <v>Cash</v>
       </c>
       <c r="L28" t="str">
-        <v>West</v>
+        <v>North</v>
       </c>
       <c r="M28" t="str">
-        <v>Basic</v>
+        <v>Premium</v>
       </c>
       <c r="N28" s="13">
-        <v>44438</v>
+        <v>44991</v>
       </c>
       <c r="O28">
-        <v>179.98</v>
+        <v>999.95</v>
       </c>
     </row>
     <row r="29" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B29" t="str">
-        <v>TRX0184</v>
+        <v>TRX0236</v>
       </c>
       <c r="C29" s="13">
-        <v>45471</v>
+        <v>45526</v>
       </c>
       <c r="D29" t="str">
-        <v>CUST57</v>
+        <v>CUST96</v>
       </c>
       <c r="E29" t="str">
-        <v>Kathleen Bennett</v>
+        <v>Cynthia Price</v>
       </c>
       <c r="F29" t="str">
-        <v>P002</v>
+        <v>P008</v>
       </c>
       <c r="G29" t="str">
-        <v>Smartphone</v>
+        <v>Bookshelf</v>
       </c>
       <c r="H29" t="str">
-        <v>Electronics</v>
+        <v>Furniture</v>
       </c>
       <c r="I29">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J29">
-        <v>699.99</v>
+        <v>149.99</v>
       </c>
       <c r="K29" t="str">
         <v>Credit Card</v>
       </c>
       <c r="L29" t="str">
-        <v>East</v>
+        <v>Central</v>
       </c>
       <c r="M29" t="str">
-        <v>Premium</v>
+        <v>Basic</v>
       </c>
       <c r="N29" s="13">
-        <v>45102</v>
+        <v>45310</v>
       </c>
       <c r="O29">
-        <v>2099.9699999999998</v>
+        <v>749.95</v>
       </c>
     </row>
     <row r="30" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B30" t="str">
-        <v>TRX0104</v>
+        <v>TRX0108</v>
       </c>
       <c r="C30" s="13">
-        <v>45471</v>
+        <v>45547</v>
       </c>
       <c r="D30" t="str">
-        <v>CUST58</v>
+        <v>CUST109</v>
       </c>
       <c r="E30" t="str">
-        <v>Patricia Moore</v>
+        <v>Dorothy Nelson</v>
       </c>
       <c r="F30" t="str">
-        <v>P001</v>
+        <v>P007</v>
       </c>
       <c r="G30" t="str">
-        <v>Laptop</v>
+        <v>Desk</v>
       </c>
       <c r="H30" t="str">
-        <v>Electronics</v>
+        <v>Furniture</v>
       </c>
       <c r="I30">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J30">
-        <v>899.99</v>
+        <v>299.99</v>
       </c>
       <c r="K30" t="str">
         <v>Credit Card</v>
       </c>
       <c r="L30" t="str">
-        <v>East</v>
+        <v>Central</v>
       </c>
       <c r="M30" t="str">
         <v>Premium</v>
       </c>
       <c r="N30" s="13">
-        <v>44993</v>
+        <v>44494</v>
       </c>
       <c r="O30">
-        <v>3599.96</v>
+        <v>899.97</v>
       </c>
     </row>
     <row r="31" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B31" t="str">
-        <v>TRX0096</v>
+        <v>TRX0054</v>
       </c>
       <c r="C31" s="13">
-        <v>45474</v>
+        <v>45551</v>
       </c>
       <c r="D31" t="str">
-        <v>CUST60</v>
+        <v>CUST113</v>
       </c>
       <c r="E31" t="str">
-        <v>Emma Wilson</v>
+        <v>Sarah Davis</v>
       </c>
       <c r="F31" t="str">
-        <v>P010</v>
+        <v>P006</v>
       </c>
       <c r="G31" t="str">
-        <v>Keyboard</v>
+        <v>Office Chair</v>
       </c>
       <c r="H31" t="str">
-        <v>Electronics</v>
+        <v>Furniture</v>
       </c>
       <c r="I31">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J31">
-        <v>89.99</v>
+        <v>199.99</v>
       </c>
       <c r="K31" t="str">
-        <v>PayPal</v>
+        <v>Debit Card</v>
       </c>
       <c r="L31" t="str">
-        <v>Central</v>
+        <v>East</v>
       </c>
       <c r="M31" t="str">
-        <v>Premium</v>
+        <v>Basic</v>
       </c>
       <c r="N31" s="13">
-        <v>45275</v>
+        <v>44458</v>
       </c>
       <c r="O31">
-        <v>179.98</v>
+        <v>799.96</v>
       </c>
     </row>
     <row r="32" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B32" t="str">
-        <v>TRX0192</v>
+        <v>TRX0119</v>
       </c>
       <c r="C32" s="13">
-        <v>45475</v>
+        <v>45560</v>
       </c>
       <c r="D32" t="str">
-        <v>CUST61</v>
+        <v>CUST118</v>
       </c>
       <c r="E32" t="str">
-        <v>Charles Allen</v>
+        <v>Linda Martin</v>
       </c>
       <c r="F32" t="str">
-        <v>P010</v>
+        <v>P008</v>
       </c>
       <c r="G32" t="str">
-        <v>Keyboard</v>
+        <v>Bookshelf</v>
       </c>
       <c r="H32" t="str">
-        <v>Electronics</v>
+        <v>Furniture</v>
       </c>
       <c r="I32">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J32">
-        <v>89.99</v>
+        <v>149.99</v>
       </c>
       <c r="K32" t="str">
         <v>PayPal</v>
       </c>
       <c r="L32" t="str">
-        <v>West</v>
+        <v>East</v>
       </c>
       <c r="M32" t="str">
-        <v>Standard</v>
+        <v>Basic</v>
       </c>
       <c r="N32" s="13">
-        <v>44802</v>
+        <v>44886</v>
       </c>
       <c r="O32">
-        <v>89.99</v>
+        <v>449.97</v>
       </c>
     </row>
     <row r="33" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B33" t="str">
-        <v>TRX0052</v>
+        <v>TRX0181</v>
       </c>
       <c r="C33" s="13">
-        <v>45476</v>
+        <v>45563</v>
       </c>
       <c r="D33" t="str">
-        <v>CUST62</v>
+        <v>CUST119</v>
       </c>
       <c r="E33" t="str">
-        <v>Susan Green</v>
+        <v>Patricia Moore</v>
       </c>
       <c r="F33" t="str">
-        <v>P010</v>
+        <v>P007</v>
       </c>
       <c r="G33" t="str">
-        <v>Keyboard</v>
+        <v>Desk</v>
       </c>
       <c r="H33" t="str">
-        <v>Electronics</v>
+        <v>Furniture</v>
       </c>
       <c r="I33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J33">
-        <v>89.99</v>
+        <v>299.99</v>
       </c>
       <c r="K33" t="str">
-        <v>Cash</v>
+        <v>Debit Card</v>
       </c>
       <c r="L33" t="str">
-        <v>South</v>
+        <v>Central</v>
       </c>
       <c r="M33" t="str">
-        <v>Standard</v>
+        <v>Basic</v>
       </c>
       <c r="N33" s="13">
-        <v>44611</v>
+        <v>44569</v>
       </c>
       <c r="O33">
-        <v>89.99</v>
+        <v>599.98</v>
       </c>
     </row>
     <row r="34" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B34" t="str">
-        <v>TRX0113</v>
+        <v>TRX0129</v>
       </c>
       <c r="C34" s="13">
-        <v>45481</v>
+        <v>45564</v>
       </c>
       <c r="D34" t="str">
-        <v>CUST65</v>
+        <v>CUST120</v>
       </c>
       <c r="E34" t="str">
-        <v>Michael Brown</v>
+        <v>Richard Lee</v>
       </c>
       <c r="F34" t="str">
-        <v>P002</v>
+        <v>P006</v>
       </c>
       <c r="G34" t="str">
-        <v>Smartphone</v>
+        <v>Office Chair</v>
       </c>
       <c r="H34" t="str">
-        <v>Electronics</v>
+        <v>Furniture</v>
       </c>
       <c r="I34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J34">
-        <v>699.99</v>
+        <v>199.99</v>
       </c>
       <c r="K34" t="str">
-        <v>PayPal</v>
+        <v>Debit Card</v>
       </c>
       <c r="L34" t="str">
         <v>East</v>
       </c>
       <c r="M34" t="str">
-        <v>Premium</v>
+        <v>Standard</v>
       </c>
       <c r="N34" s="13">
-        <v>45389</v>
+        <v>44953</v>
       </c>
       <c r="O34">
-        <v>1399.98</v>
+        <v>199.99</v>
       </c>
     </row>
     <row r="35" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B35" t="str">
-        <v>TRX0114</v>
+        <v>TRX0174</v>
       </c>
       <c r="C35" s="13">
-        <v>45481</v>
+        <v>45566</v>
       </c>
       <c r="D35" t="str">
-        <v>CUST66</v>
+        <v>CUST121</v>
       </c>
       <c r="E35" t="str">
-        <v>Barbara Young</v>
+        <v>Michael Brown</v>
       </c>
       <c r="F35" t="str">
-        <v>P010</v>
+        <v>P007</v>
       </c>
       <c r="G35" t="str">
-        <v>Keyboard</v>
+        <v>Desk</v>
       </c>
       <c r="H35" t="str">
-        <v>Electronics</v>
+        <v>Furniture</v>
       </c>
       <c r="I35">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J35">
-        <v>89.99</v>
+        <v>299.99</v>
       </c>
       <c r="K35" t="str">
-        <v>Debit Card</v>
+        <v>Cash</v>
       </c>
       <c r="L35" t="str">
-        <v>North</v>
+        <v>Central</v>
       </c>
       <c r="M35" t="str">
         <v>Premium</v>
       </c>
       <c r="N35" s="13">
-        <v>45161</v>
+        <v>44460</v>
       </c>
       <c r="O35">
-        <v>449.95</v>
+        <v>1199.96</v>
       </c>
     </row>
     <row r="36" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B36" t="str">
-        <v>TRX0018</v>
+        <v>TRX0218</v>
       </c>
       <c r="C36" s="13">
-        <v>45484</v>
+        <v>45573</v>
       </c>
       <c r="D36" t="str">
-        <v>CUST68</v>
+        <v>CUST125</v>
       </c>
       <c r="E36" t="str">
-        <v>Joseph Jackson</v>
+        <v>Carol Evans</v>
       </c>
       <c r="F36" t="str">
-        <v>P003</v>
+        <v>P008</v>
       </c>
       <c r="G36" t="str">
-        <v>Headphones</v>
+        <v>Bookshelf</v>
       </c>
       <c r="H36" t="str">
-        <v>Electronics</v>
+        <v>Furniture</v>
       </c>
       <c r="I36">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J36">
         <v>149.99</v>
       </c>
       <c r="K36" t="str">
-        <v>Cash</v>
+        <v>Credit Card</v>
       </c>
       <c r="L36" t="str">
-        <v>Central</v>
+        <v>South</v>
       </c>
       <c r="M36" t="str">
         <v>Standard</v>
       </c>
       <c r="N36" s="13">
-        <v>44909</v>
+        <v>44940</v>
       </c>
       <c r="O36">
-        <v>149.99</v>
+        <v>449.97</v>
       </c>
     </row>
     <row r="37" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B37" t="str">
-        <v>TRX0162</v>
+        <v>TRX0085</v>
       </c>
       <c r="C37" s="13">
-        <v>45496</v>
+        <v>45576</v>
       </c>
       <c r="D37" t="str">
-        <v>CUST74</v>
+        <v>CUST126</v>
       </c>
       <c r="E37" t="str">
-        <v>Sharon Butler</v>
+        <v>Daniel King</v>
       </c>
       <c r="F37" t="str">
-        <v>P001</v>
+        <v>P007</v>
       </c>
       <c r="G37" t="str">
-        <v>Laptop</v>
+        <v>Desk</v>
       </c>
       <c r="H37" t="str">
-        <v>Electronics</v>
+        <v>Furniture</v>
       </c>
       <c r="I37">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J37">
-        <v>899.99</v>
+        <v>299.99</v>
       </c>
       <c r="K37" t="str">
-        <v>Cash</v>
+        <v>Credit Card</v>
       </c>
       <c r="L37" t="str">
         <v>Central</v>
@@ -65476,42 +65418,42 @@
         <v>Standard</v>
       </c>
       <c r="N37" s="13">
-        <v>45179</v>
+        <v>45174</v>
       </c>
       <c r="O37">
-        <v>899.99</v>
+        <v>899.97</v>
       </c>
     </row>
     <row r="38" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B38" t="str">
-        <v>TRX0244</v>
+        <v>TRX0017</v>
       </c>
       <c r="C38" s="13">
-        <v>45497</v>
+        <v>45600</v>
       </c>
       <c r="D38" t="str">
-        <v>CUST75</v>
+        <v>CUST138</v>
       </c>
       <c r="E38" t="str">
-        <v>Joseph Jackson</v>
+        <v>Karen Hill</v>
       </c>
       <c r="F38" t="str">
-        <v>P001</v>
+        <v>P007</v>
       </c>
       <c r="G38" t="str">
-        <v>Laptop</v>
+        <v>Desk</v>
       </c>
       <c r="H38" t="str">
-        <v>Electronics</v>
+        <v>Furniture</v>
       </c>
       <c r="I38">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J38">
-        <v>899.99</v>
+        <v>299.99</v>
       </c>
       <c r="K38" t="str">
-        <v>Debit Card</v>
+        <v>Credit Card</v>
       </c>
       <c r="L38" t="str">
         <v>South</v>
@@ -65520,218 +65462,218 @@
         <v>Standard</v>
       </c>
       <c r="N38" s="13">
-        <v>44899</v>
+        <v>44502</v>
       </c>
       <c r="O38">
-        <v>4499.95</v>
+        <v>899.97</v>
       </c>
     </row>
     <row r="39" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B39" t="str">
-        <v>TRX0215</v>
+        <v>TRX0109</v>
       </c>
       <c r="C39" s="13">
-        <v>45498</v>
+        <v>45604</v>
       </c>
       <c r="D39" t="str">
-        <v>CUST77</v>
+        <v>CUST140</v>
       </c>
       <c r="E39" t="str">
-        <v>Gerald Murphy</v>
+        <v>Maria Garcia</v>
       </c>
       <c r="F39" t="str">
-        <v>P009</v>
+        <v>P008</v>
       </c>
       <c r="G39" t="str">
-        <v>Monitor</v>
+        <v>Bookshelf</v>
       </c>
       <c r="H39" t="str">
-        <v>Electronics</v>
+        <v>Furniture</v>
       </c>
       <c r="I39">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J39">
-        <v>249.99</v>
+        <v>149.99</v>
       </c>
       <c r="K39" t="str">
-        <v>Debit Card</v>
+        <v>Credit Card</v>
       </c>
       <c r="L39" t="str">
-        <v>Central</v>
+        <v>West</v>
       </c>
       <c r="M39" t="str">
-        <v>Standard</v>
+        <v>Premium</v>
       </c>
       <c r="N39" s="13">
-        <v>45127</v>
+        <v>44848</v>
       </c>
       <c r="O39">
-        <v>999.96</v>
+        <v>299.98</v>
       </c>
     </row>
     <row r="40" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B40" t="str">
-        <v>TRX0080</v>
+        <v>TRX0210</v>
       </c>
       <c r="C40" s="13">
-        <v>45500</v>
+        <v>45608</v>
       </c>
       <c r="D40" t="str">
-        <v>CUST78</v>
+        <v>CUST145</v>
       </c>
       <c r="E40" t="str">
-        <v>Barbara Young</v>
+        <v>Sarah Davis</v>
       </c>
       <c r="F40" t="str">
-        <v>P009</v>
+        <v>P008</v>
       </c>
       <c r="G40" t="str">
-        <v>Monitor</v>
+        <v>Bookshelf</v>
       </c>
       <c r="H40" t="str">
-        <v>Electronics</v>
+        <v>Furniture</v>
       </c>
       <c r="I40">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J40">
-        <v>249.99</v>
+        <v>149.99</v>
       </c>
       <c r="K40" t="str">
-        <v>Cash</v>
+        <v>PayPal</v>
       </c>
       <c r="L40" t="str">
-        <v>North</v>
+        <v>Central</v>
       </c>
       <c r="M40" t="str">
-        <v>Premium</v>
+        <v>Basic</v>
       </c>
       <c r="N40" s="13">
-        <v>45164</v>
+        <v>44901</v>
       </c>
       <c r="O40">
-        <v>499.98</v>
+        <v>749.95</v>
       </c>
     </row>
     <row r="41" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B41" t="str">
-        <v>TRX0157</v>
+        <v>TRX0073</v>
       </c>
       <c r="C41" s="13">
-        <v>45501</v>
+        <v>45613</v>
       </c>
       <c r="D41" t="str">
-        <v>CUST80</v>
+        <v>CUST147</v>
       </c>
       <c r="E41" t="str">
-        <v>Mark Carter</v>
+        <v>Sandra Phillips</v>
       </c>
       <c r="F41" t="str">
-        <v>P010</v>
+        <v>P008</v>
       </c>
       <c r="G41" t="str">
-        <v>Keyboard</v>
+        <v>Bookshelf</v>
       </c>
       <c r="H41" t="str">
-        <v>Electronics</v>
+        <v>Furniture</v>
       </c>
       <c r="I41">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J41">
-        <v>89.99</v>
+        <v>149.99</v>
       </c>
       <c r="K41" t="str">
-        <v>PayPal</v>
+        <v>Cash</v>
       </c>
       <c r="L41" t="str">
-        <v>South</v>
+        <v>North</v>
       </c>
       <c r="M41" t="str">
         <v>Basic</v>
       </c>
       <c r="N41" s="13">
-        <v>44976</v>
+        <v>44869</v>
       </c>
       <c r="O41">
-        <v>179.98</v>
+        <v>749.95</v>
       </c>
     </row>
     <row r="42" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B42" t="str">
-        <v>TRX0217</v>
+        <v>TRX0160</v>
       </c>
       <c r="C42" s="13">
-        <v>45503</v>
+        <v>45617</v>
       </c>
       <c r="D42" t="str">
-        <v>CUST82</v>
+        <v>CUST149</v>
       </c>
       <c r="E42" t="str">
-        <v>Mark Carter</v>
+        <v>Edward Mitchell</v>
       </c>
       <c r="F42" t="str">
-        <v>P002</v>
+        <v>P006</v>
       </c>
       <c r="G42" t="str">
-        <v>Smartphone</v>
+        <v>Office Chair</v>
       </c>
       <c r="H42" t="str">
-        <v>Electronics</v>
+        <v>Furniture</v>
       </c>
       <c r="I42">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J42">
-        <v>699.99</v>
+        <v>199.99</v>
       </c>
       <c r="K42" t="str">
-        <v>Credit Card</v>
+        <v>Debit Card</v>
       </c>
       <c r="L42" t="str">
-        <v>North</v>
+        <v>Central</v>
       </c>
       <c r="M42" t="str">
         <v>Premium</v>
       </c>
       <c r="N42" s="13">
-        <v>44999</v>
+        <v>44427</v>
       </c>
       <c r="O42">
-        <v>1399.98</v>
+        <v>799.96</v>
       </c>
     </row>
     <row r="43" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B43" t="str">
-        <v>TRX0249</v>
+        <v>TRX0206</v>
       </c>
       <c r="C43" s="13">
-        <v>45504</v>
+        <v>45623</v>
       </c>
       <c r="D43" t="str">
-        <v>CUST83</v>
+        <v>CUST153</v>
       </c>
       <c r="E43" t="str">
-        <v>Helen Roberts</v>
+        <v>Linda Martin</v>
       </c>
       <c r="F43" t="str">
-        <v>P001</v>
+        <v>P008</v>
       </c>
       <c r="G43" t="str">
-        <v>Laptop</v>
+        <v>Bookshelf</v>
       </c>
       <c r="H43" t="str">
-        <v>Electronics</v>
+        <v>Furniture</v>
       </c>
       <c r="I43">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J43">
-        <v>899.99</v>
+        <v>149.99</v>
       </c>
       <c r="K43" t="str">
-        <v>Debit Card</v>
+        <v>Cash</v>
       </c>
       <c r="L43" t="str">
         <v>South</v>
@@ -65740,80 +65682,80 @@
         <v>Standard</v>
       </c>
       <c r="N43" s="13">
-        <v>44523</v>
+        <v>45101</v>
       </c>
       <c r="O43">
-        <v>3599.96</v>
+        <v>299.98</v>
       </c>
     </row>
     <row r="44" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B44" t="str">
-        <v>TRX0101</v>
+        <v>TRX0045</v>
       </c>
       <c r="C44" s="13">
-        <v>45513</v>
+        <v>45627</v>
       </c>
       <c r="D44" t="str">
-        <v>CUST86</v>
+        <v>CUST154</v>
       </c>
       <c r="E44" t="str">
-        <v>Maria Garcia</v>
+        <v>Kevin Scott</v>
       </c>
       <c r="F44" t="str">
-        <v>P010</v>
+        <v>P007</v>
       </c>
       <c r="G44" t="str">
-        <v>Keyboard</v>
+        <v>Desk</v>
       </c>
       <c r="H44" t="str">
-        <v>Electronics</v>
+        <v>Furniture</v>
       </c>
       <c r="I44">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J44">
-        <v>89.99</v>
+        <v>299.99</v>
       </c>
       <c r="K44" t="str">
-        <v>Credit Card</v>
+        <v>Cash</v>
       </c>
       <c r="L44" t="str">
-        <v>North</v>
+        <v>South</v>
       </c>
       <c r="M44" t="str">
-        <v>Standard</v>
+        <v>Premium</v>
       </c>
       <c r="N44" s="13">
-        <v>45393</v>
+        <v>44659</v>
       </c>
       <c r="O44">
-        <v>89.99</v>
+        <v>899.97</v>
       </c>
     </row>
     <row r="45" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B45" t="str">
-        <v>TRX0020</v>
+        <v>TRX0081</v>
       </c>
       <c r="C45" s="13">
-        <v>45517</v>
+        <v>45641</v>
       </c>
       <c r="D45" t="str">
-        <v>CUST88</v>
+        <v>CUST165</v>
       </c>
       <c r="E45" t="str">
         <v>David Martinez</v>
       </c>
       <c r="F45" t="str">
-        <v>P003</v>
+        <v>P008</v>
       </c>
       <c r="G45" t="str">
-        <v>Headphones</v>
+        <v>Bookshelf</v>
       </c>
       <c r="H45" t="str">
-        <v>Electronics</v>
+        <v>Furniture</v>
       </c>
       <c r="I45">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J45">
         <v>149.99</v>
@@ -65822,48 +65764,48 @@
         <v>Debit Card</v>
       </c>
       <c r="L45" t="str">
-        <v>South</v>
+        <v>East</v>
       </c>
       <c r="M45" t="str">
-        <v>Premium</v>
+        <v>Standard</v>
       </c>
       <c r="N45" s="13">
-        <v>44820</v>
+        <v>45200</v>
       </c>
       <c r="O45">
-        <v>599.96</v>
+        <v>149.99</v>
       </c>
     </row>
     <row r="46" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B46" t="str">
-        <v>TRX0075</v>
+        <v>TRX0224</v>
       </c>
       <c r="C46" s="13">
-        <v>45517</v>
+        <v>45641</v>
       </c>
       <c r="D46" t="str">
-        <v>CUST89</v>
+        <v>CUST166</v>
       </c>
       <c r="E46" t="str">
-        <v>Margaret Wright</v>
+        <v>Steven Turner</v>
       </c>
       <c r="F46" t="str">
-        <v>P009</v>
+        <v>P007</v>
       </c>
       <c r="G46" t="str">
-        <v>Monitor</v>
+        <v>Desk</v>
       </c>
       <c r="H46" t="str">
-        <v>Electronics</v>
+        <v>Furniture</v>
       </c>
       <c r="I46">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J46">
-        <v>249.99</v>
+        <v>299.99</v>
       </c>
       <c r="K46" t="str">
-        <v>PayPal</v>
+        <v>Cash</v>
       </c>
       <c r="L46" t="str">
         <v>East</v>
@@ -65872,259 +65814,259 @@
         <v>Premium</v>
       </c>
       <c r="N46" s="13">
-        <v>44782</v>
+        <v>44724</v>
       </c>
       <c r="O46">
-        <v>1249.95</v>
+        <v>599.98</v>
       </c>
     </row>
     <row r="47" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B47" t="str">
-        <v>TRX0098</v>
+        <v>TRX0046</v>
       </c>
       <c r="C47" s="13">
-        <v>45517</v>
+        <v>45646</v>
       </c>
       <c r="D47" t="str">
-        <v>CUST90</v>
+        <v>CUST170</v>
       </c>
       <c r="E47" t="str">
-        <v>Karen Hill</v>
+        <v>Michael Brown</v>
       </c>
       <c r="F47" t="str">
-        <v>P009</v>
+        <v>P008</v>
       </c>
       <c r="G47" t="str">
-        <v>Monitor</v>
+        <v>Bookshelf</v>
       </c>
       <c r="H47" t="str">
-        <v>Electronics</v>
+        <v>Furniture</v>
       </c>
       <c r="I47">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J47">
-        <v>249.99</v>
+        <v>149.99</v>
       </c>
       <c r="K47" t="str">
-        <v>PayPal</v>
+        <v>Cash</v>
       </c>
       <c r="L47" t="str">
-        <v>North</v>
+        <v>South</v>
       </c>
       <c r="M47" t="str">
-        <v>Premium</v>
+        <v>Basic</v>
       </c>
       <c r="N47" s="13">
-        <v>44465</v>
+        <v>45239</v>
       </c>
       <c r="O47">
-        <v>749.97</v>
+        <v>299.98</v>
       </c>
     </row>
     <row r="48" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B48" t="str">
-        <v>TRX0140</v>
+        <v>TRX0008</v>
       </c>
       <c r="C48" s="13">
-        <v>45522</v>
+        <v>45648</v>
       </c>
       <c r="D48" t="str">
-        <v>CUST93</v>
+        <v>CUST172</v>
       </c>
       <c r="E48" t="str">
-        <v>Mark Carter</v>
+        <v>David Martinez</v>
       </c>
       <c r="F48" t="str">
-        <v>P010</v>
+        <v>P008</v>
       </c>
       <c r="G48" t="str">
-        <v>Keyboard</v>
+        <v>Bookshelf</v>
       </c>
       <c r="H48" t="str">
-        <v>Electronics</v>
+        <v>Furniture</v>
       </c>
       <c r="I48">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J48">
-        <v>89.99</v>
+        <v>149.99</v>
       </c>
       <c r="K48" t="str">
-        <v>Cash</v>
+        <v>Debit Card</v>
       </c>
       <c r="L48" t="str">
-        <v>East</v>
+        <v>North</v>
       </c>
       <c r="M48" t="str">
-        <v>Premium</v>
+        <v>Standard</v>
       </c>
       <c r="N48" s="13">
-        <v>44972</v>
+        <v>44522</v>
       </c>
       <c r="O48">
-        <v>179.98</v>
+        <v>449.97</v>
       </c>
     </row>
     <row r="49" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B49" t="str">
-        <v>TRX0132</v>
+        <v>TRX0171</v>
       </c>
       <c r="C49" s="13">
-        <v>45523</v>
+        <v>45649</v>
       </c>
       <c r="D49" t="str">
-        <v>CUST94</v>
+        <v>CUST173</v>
       </c>
       <c r="E49" t="str">
-        <v>Gerald Murphy</v>
+        <v>Kevin Scott</v>
       </c>
       <c r="F49" t="str">
-        <v>P001</v>
+        <v>P007</v>
       </c>
       <c r="G49" t="str">
-        <v>Laptop</v>
+        <v>Desk</v>
       </c>
       <c r="H49" t="str">
-        <v>Electronics</v>
+        <v>Furniture</v>
       </c>
       <c r="I49">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J49">
-        <v>899.99</v>
+        <v>299.99</v>
       </c>
       <c r="K49" t="str">
-        <v>Debit Card</v>
+        <v>PayPal</v>
       </c>
       <c r="L49" t="str">
-        <v>East</v>
+        <v>South</v>
       </c>
       <c r="M49" t="str">
         <v>Basic</v>
       </c>
       <c r="N49" s="13">
-        <v>44526</v>
+        <v>44721</v>
       </c>
       <c r="O49">
-        <v>4499.95</v>
+        <v>599.98</v>
       </c>
     </row>
     <row r="50" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B50" t="str">
-        <v>TRX0031</v>
+        <v>TRX0143</v>
       </c>
       <c r="C50" s="13">
-        <v>45523</v>
+        <v>45654</v>
       </c>
       <c r="D50" t="str">
-        <v>CUST95</v>
+        <v>CUST174</v>
       </c>
       <c r="E50" t="str">
-        <v>Nancy Collins</v>
+        <v>Michael Brown</v>
       </c>
       <c r="F50" t="str">
-        <v>P003</v>
+        <v>P007</v>
       </c>
       <c r="G50" t="str">
-        <v>Headphones</v>
+        <v>Desk</v>
       </c>
       <c r="H50" t="str">
-        <v>Electronics</v>
+        <v>Furniture</v>
       </c>
       <c r="I50">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J50">
-        <v>149.99</v>
+        <v>299.99</v>
       </c>
       <c r="K50" t="str">
-        <v>PayPal</v>
+        <v>Cash</v>
       </c>
       <c r="L50" t="str">
-        <v>East</v>
+        <v>West</v>
       </c>
       <c r="M50" t="str">
         <v>Basic</v>
       </c>
       <c r="N50" s="13">
-        <v>44574</v>
+        <v>44771</v>
       </c>
       <c r="O50">
-        <v>449.97</v>
+        <v>599.98</v>
       </c>
     </row>
     <row r="51" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B51" t="str">
-        <v>TRX0037</v>
+        <v>TRX0165</v>
       </c>
       <c r="C51" s="13">
-        <v>45528</v>
+        <v>45654</v>
       </c>
       <c r="D51" t="str">
-        <v>CUST98</v>
+        <v>CUST175</v>
       </c>
       <c r="E51" t="str">
-        <v>Harry Morgan</v>
+        <v>Helen Roberts</v>
       </c>
       <c r="F51" t="str">
-        <v>P009</v>
+        <v>P006</v>
       </c>
       <c r="G51" t="str">
-        <v>Monitor</v>
+        <v>Office Chair</v>
       </c>
       <c r="H51" t="str">
-        <v>Electronics</v>
+        <v>Furniture</v>
       </c>
       <c r="I51">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J51">
-        <v>249.99</v>
+        <v>199.99</v>
       </c>
       <c r="K51" t="str">
-        <v>Cash</v>
+        <v>Credit Card</v>
       </c>
       <c r="L51" t="str">
-        <v>South</v>
+        <v>Central</v>
       </c>
       <c r="M51" t="str">
-        <v>Standard</v>
+        <v>Basic</v>
       </c>
       <c r="N51" s="13">
-        <v>44572</v>
+        <v>44523</v>
       </c>
       <c r="O51">
-        <v>499.98</v>
+        <v>799.96</v>
       </c>
     </row>
     <row r="52" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B52" t="str">
-        <v>TRX0058</v>
+        <v>TRX0147</v>
       </c>
       <c r="C52" s="13">
-        <v>45532</v>
+        <v>45655</v>
       </c>
       <c r="D52" t="str">
-        <v>CUST99</v>
+        <v>CUST177</v>
       </c>
       <c r="E52" t="str">
-        <v>Gerald Murphy</v>
+        <v>Nancy Collins</v>
       </c>
       <c r="F52" t="str">
-        <v>P002</v>
+        <v>P008</v>
       </c>
       <c r="G52" t="str">
-        <v>Smartphone</v>
+        <v>Bookshelf</v>
       </c>
       <c r="H52" t="str">
-        <v>Electronics</v>
+        <v>Furniture</v>
       </c>
       <c r="I52">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J52">
-        <v>699.99</v>
+        <v>149.99</v>
       </c>
       <c r="K52" t="str">
         <v>Cash</v>
@@ -66136,825 +66078,825 @@
         <v>Premium</v>
       </c>
       <c r="N52" s="13">
-        <v>44497</v>
+        <v>45347</v>
       </c>
       <c r="O52">
-        <v>699.99</v>
+        <v>749.95</v>
       </c>
     </row>
     <row r="53" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B53" t="str">
-        <v>TRX0170</v>
+        <v>TRX0091</v>
       </c>
       <c r="C53" s="13">
-        <v>45532</v>
+        <v>45663</v>
       </c>
       <c r="D53" t="str">
-        <v>CUST100</v>
+        <v>CUST182</v>
       </c>
       <c r="E53" t="str">
-        <v>Carol Evans</v>
+        <v>Michael Brown</v>
       </c>
       <c r="F53" t="str">
-        <v>P003</v>
+        <v>P007</v>
       </c>
       <c r="G53" t="str">
-        <v>Headphones</v>
+        <v>Desk</v>
       </c>
       <c r="H53" t="str">
-        <v>Electronics</v>
+        <v>Furniture</v>
       </c>
       <c r="I53">
         <v>3</v>
       </c>
       <c r="J53">
-        <v>149.99</v>
+        <v>299.99</v>
       </c>
       <c r="K53" t="str">
         <v>Cash</v>
       </c>
       <c r="L53" t="str">
-        <v>West</v>
+        <v>South</v>
       </c>
       <c r="M53" t="str">
-        <v>Premium</v>
+        <v>Standard</v>
       </c>
       <c r="N53" s="13">
-        <v>45212</v>
+        <v>44422</v>
       </c>
       <c r="O53">
-        <v>449.97</v>
+        <v>899.97</v>
       </c>
     </row>
     <row r="54" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B54" t="str">
-        <v>TRX0248</v>
+        <v>TRX0223</v>
       </c>
       <c r="C54" s="13">
-        <v>45534</v>
+        <v>45667</v>
       </c>
       <c r="D54" t="str">
-        <v>CUST101</v>
+        <v>CUST184</v>
       </c>
       <c r="E54" t="str">
-        <v>Sandra Phillips</v>
+        <v>Nancy Collins</v>
       </c>
       <c r="F54" t="str">
-        <v>P002</v>
+        <v>P006</v>
       </c>
       <c r="G54" t="str">
-        <v>Smartphone</v>
+        <v>Office Chair</v>
       </c>
       <c r="H54" t="str">
-        <v>Electronics</v>
+        <v>Furniture</v>
       </c>
       <c r="I54">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J54">
-        <v>699.99</v>
+        <v>199.99</v>
       </c>
       <c r="K54" t="str">
-        <v>Credit Card</v>
+        <v>PayPal</v>
       </c>
       <c r="L54" t="str">
-        <v>North</v>
+        <v>Central</v>
       </c>
       <c r="M54" t="str">
-        <v>Premium</v>
+        <v>Standard</v>
       </c>
       <c r="N54" s="13">
-        <v>44421</v>
+        <v>44633</v>
       </c>
       <c r="O54">
-        <v>1399.98</v>
+        <v>999.95</v>
       </c>
     </row>
     <row r="55" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B55" t="str">
-        <v>TRX0099</v>
+        <v>TRX0022</v>
       </c>
       <c r="C55" s="13">
-        <v>45537</v>
+        <v>45670</v>
       </c>
       <c r="D55" t="str">
-        <v>CUST102</v>
+        <v>CUST189</v>
       </c>
       <c r="E55" t="str">
-        <v>Carol Evans</v>
+        <v>Mark Carter</v>
       </c>
       <c r="F55" t="str">
-        <v>P009</v>
+        <v>P007</v>
       </c>
       <c r="G55" t="str">
-        <v>Monitor</v>
+        <v>Desk</v>
       </c>
       <c r="H55" t="str">
-        <v>Electronics</v>
+        <v>Furniture</v>
       </c>
       <c r="I55">
         <v>1</v>
       </c>
       <c r="J55">
-        <v>249.99</v>
+        <v>299.99</v>
       </c>
       <c r="K55" t="str">
         <v>Credit Card</v>
       </c>
       <c r="L55" t="str">
-        <v>West</v>
+        <v>North</v>
       </c>
       <c r="M55" t="str">
-        <v>Premium</v>
+        <v>Basic</v>
       </c>
       <c r="N55" s="13">
-        <v>44685</v>
+        <v>44436</v>
       </c>
       <c r="O55">
-        <v>249.99</v>
+        <v>299.99</v>
       </c>
     </row>
     <row r="56" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B56" t="str">
-        <v>TRX0074</v>
+        <v>TRX0051</v>
       </c>
       <c r="C56" s="13">
-        <v>45537</v>
+        <v>45671</v>
       </c>
       <c r="D56" t="str">
-        <v>CUST103</v>
+        <v>CUST192</v>
       </c>
       <c r="E56" t="str">
-        <v>Paul Baker</v>
+        <v>Sandra Phillips</v>
       </c>
       <c r="F56" t="str">
-        <v>P009</v>
+        <v>P007</v>
       </c>
       <c r="G56" t="str">
-        <v>Monitor</v>
+        <v>Desk</v>
       </c>
       <c r="H56" t="str">
-        <v>Electronics</v>
+        <v>Furniture</v>
       </c>
       <c r="I56">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J56">
-        <v>249.99</v>
+        <v>299.99</v>
       </c>
       <c r="K56" t="str">
-        <v>Debit Card</v>
+        <v>Credit Card</v>
       </c>
       <c r="L56" t="str">
-        <v>North</v>
+        <v>South</v>
       </c>
       <c r="M56" t="str">
-        <v>Premium</v>
+        <v>Basic</v>
       </c>
       <c r="N56" s="13">
-        <v>45332</v>
+        <v>45204</v>
       </c>
       <c r="O56">
-        <v>249.99</v>
+        <v>899.97</v>
       </c>
     </row>
     <row r="57" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B57" t="str">
-        <v>TRX0225</v>
+        <v>TRX0106</v>
       </c>
       <c r="C57" s="13">
-        <v>45538</v>
+        <v>45673</v>
       </c>
       <c r="D57" t="str">
-        <v>CUST104</v>
+        <v>CUST193</v>
       </c>
       <c r="E57" t="str">
         <v>Lawrence Reed</v>
       </c>
       <c r="F57" t="str">
-        <v>P002</v>
+        <v>P006</v>
       </c>
       <c r="G57" t="str">
-        <v>Smartphone</v>
+        <v>Office Chair</v>
       </c>
       <c r="H57" t="str">
-        <v>Electronics</v>
+        <v>Furniture</v>
       </c>
       <c r="I57">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J57">
-        <v>699.99</v>
+        <v>199.99</v>
       </c>
       <c r="K57" t="str">
         <v>Debit Card</v>
       </c>
       <c r="L57" t="str">
-        <v>Central</v>
+        <v>South</v>
       </c>
       <c r="M57" t="str">
-        <v>Premium</v>
+        <v>Standard</v>
       </c>
       <c r="N57" s="13">
-        <v>44870</v>
+        <v>44544</v>
       </c>
       <c r="O57">
-        <v>1399.98</v>
+        <v>799.96</v>
       </c>
     </row>
     <row r="58" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B58" t="str">
-        <v>TRX0211</v>
+        <v>TRX0059</v>
       </c>
       <c r="C58" s="13">
-        <v>45548</v>
+        <v>45673</v>
       </c>
       <c r="D58" t="str">
-        <v>CUST110</v>
+        <v>CUST194</v>
       </c>
       <c r="E58" t="str">
-        <v>Kathleen Bennett</v>
+        <v>Elizabeth Hall</v>
       </c>
       <c r="F58" t="str">
-        <v>P010</v>
+        <v>P007</v>
       </c>
       <c r="G58" t="str">
-        <v>Keyboard</v>
+        <v>Desk</v>
       </c>
       <c r="H58" t="str">
-        <v>Electronics</v>
+        <v>Furniture</v>
       </c>
       <c r="I58">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J58">
-        <v>89.99</v>
+        <v>299.99</v>
       </c>
       <c r="K58" t="str">
-        <v>Credit Card</v>
+        <v>Debit Card</v>
       </c>
       <c r="L58" t="str">
-        <v>South</v>
+        <v>Central</v>
       </c>
       <c r="M58" t="str">
-        <v>Premium</v>
+        <v>Basic</v>
       </c>
       <c r="N58" s="13">
-        <v>44641</v>
+        <v>44431</v>
       </c>
       <c r="O58">
-        <v>179.98</v>
+        <v>1499.95</v>
       </c>
     </row>
     <row r="59" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B59" t="str">
-        <v>TRX0005</v>
+        <v>TRX0072</v>
       </c>
       <c r="C59" s="13">
-        <v>45550</v>
+        <v>45673</v>
       </c>
       <c r="D59" t="str">
-        <v>CUST111</v>
+        <v>CUST195</v>
       </c>
       <c r="E59" t="str">
-        <v>Ruth Brooks</v>
+        <v>Robert Thomas</v>
       </c>
       <c r="F59" t="str">
-        <v>P003</v>
+        <v>P008</v>
       </c>
       <c r="G59" t="str">
-        <v>Headphones</v>
+        <v>Bookshelf</v>
       </c>
       <c r="H59" t="str">
-        <v>Electronics</v>
+        <v>Furniture</v>
       </c>
       <c r="I59">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J59">
         <v>149.99</v>
       </c>
       <c r="K59" t="str">
-        <v>Cash</v>
+        <v>Credit Card</v>
       </c>
       <c r="L59" t="str">
-        <v>North</v>
+        <v>East</v>
       </c>
       <c r="M59" t="str">
-        <v>Basic</v>
+        <v>Standard</v>
       </c>
       <c r="N59" s="13">
-        <v>44909</v>
+        <v>44395</v>
       </c>
       <c r="O59">
-        <v>599.96</v>
+        <v>449.97</v>
       </c>
     </row>
     <row r="60" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B60" t="str">
-        <v>TRX0195</v>
+        <v>TRX0178</v>
       </c>
       <c r="C60" s="13">
-        <v>45551</v>
+        <v>45686</v>
       </c>
       <c r="D60" t="str">
-        <v>CUST112</v>
+        <v>CUST200</v>
       </c>
       <c r="E60" t="str">
-        <v>Karen Hill</v>
+        <v>Mark Carter</v>
       </c>
       <c r="F60" t="str">
-        <v>P009</v>
+        <v>P007</v>
       </c>
       <c r="G60" t="str">
-        <v>Monitor</v>
+        <v>Desk</v>
       </c>
       <c r="H60" t="str">
-        <v>Electronics</v>
+        <v>Furniture</v>
       </c>
       <c r="I60">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J60">
-        <v>249.99</v>
+        <v>299.99</v>
       </c>
       <c r="K60" t="str">
-        <v>PayPal</v>
+        <v>Debit Card</v>
       </c>
       <c r="L60" t="str">
-        <v>South</v>
+        <v>West</v>
       </c>
       <c r="M60" t="str">
-        <v>Basic</v>
+        <v>Standard</v>
       </c>
       <c r="N60" s="13">
-        <v>44993</v>
+        <v>44952</v>
       </c>
       <c r="O60">
-        <v>499.98</v>
+        <v>899.97</v>
       </c>
     </row>
     <row r="61" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B61" t="str">
-        <v>TRX0077</v>
+        <v>TRX0024</v>
       </c>
       <c r="C61" s="13">
-        <v>45554</v>
+        <v>45695</v>
       </c>
       <c r="D61" t="str">
-        <v>CUST114</v>
+        <v>CUST206</v>
       </c>
       <c r="E61" t="str">
-        <v>Daniel King</v>
+        <v>Ruth Brooks</v>
       </c>
       <c r="F61" t="str">
-        <v>P010</v>
+        <v>P008</v>
       </c>
       <c r="G61" t="str">
-        <v>Keyboard</v>
+        <v>Bookshelf</v>
       </c>
       <c r="H61" t="str">
-        <v>Electronics</v>
+        <v>Furniture</v>
       </c>
       <c r="I61">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J61">
-        <v>89.99</v>
+        <v>149.99</v>
       </c>
       <c r="K61" t="str">
-        <v>Credit Card</v>
+        <v>Debit Card</v>
       </c>
       <c r="L61" t="str">
-        <v>East</v>
+        <v>North</v>
       </c>
       <c r="M61" t="str">
         <v>Premium</v>
       </c>
       <c r="N61" s="13">
-        <v>44446</v>
+        <v>44564</v>
       </c>
       <c r="O61">
-        <v>449.95</v>
+        <v>449.97</v>
       </c>
     </row>
     <row r="62" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B62" t="str">
-        <v>TRX0111</v>
+        <v>TRX0105</v>
       </c>
       <c r="C62" s="13">
-        <v>45554</v>
+        <v>45695</v>
       </c>
       <c r="D62" t="str">
-        <v>CUST115</v>
+        <v>CUST207</v>
       </c>
       <c r="E62" t="str">
-        <v>William White</v>
+        <v>Virginia Sanders</v>
       </c>
       <c r="F62" t="str">
-        <v>P003</v>
+        <v>P007</v>
       </c>
       <c r="G62" t="str">
-        <v>Headphones</v>
+        <v>Desk</v>
       </c>
       <c r="H62" t="str">
-        <v>Electronics</v>
+        <v>Furniture</v>
       </c>
       <c r="I62">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J62">
-        <v>149.99</v>
+        <v>299.99</v>
       </c>
       <c r="K62" t="str">
-        <v>PayPal</v>
+        <v>Credit Card</v>
       </c>
       <c r="L62" t="str">
-        <v>East</v>
+        <v>South</v>
       </c>
       <c r="M62" t="str">
-        <v>Standard</v>
+        <v>Basic</v>
       </c>
       <c r="N62" s="13">
-        <v>44482</v>
+        <v>44959</v>
       </c>
       <c r="O62">
-        <v>149.99</v>
+        <v>1499.95</v>
       </c>
     </row>
     <row r="63" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B63" t="str">
-        <v>TRX0123</v>
+        <v>TRX0089</v>
       </c>
       <c r="C63" s="13">
-        <v>45554</v>
+        <v>45704</v>
       </c>
       <c r="D63" t="str">
-        <v>CUST116</v>
+        <v>CUST210</v>
       </c>
       <c r="E63" t="str">
-        <v>Peter Richardson</v>
+        <v>Kevin Scott</v>
       </c>
       <c r="F63" t="str">
-        <v>P002</v>
+        <v>P006</v>
       </c>
       <c r="G63" t="str">
-        <v>Smartphone</v>
+        <v>Office Chair</v>
       </c>
       <c r="H63" t="str">
-        <v>Electronics</v>
+        <v>Furniture</v>
       </c>
       <c r="I63">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J63">
-        <v>699.99</v>
+        <v>199.99</v>
       </c>
       <c r="K63" t="str">
-        <v>PayPal</v>
+        <v>Cash</v>
       </c>
       <c r="L63" t="str">
-        <v>South</v>
+        <v>Central</v>
       </c>
       <c r="M63" t="str">
         <v>Basic</v>
       </c>
       <c r="N63" s="13">
-        <v>44618</v>
+        <v>44735</v>
       </c>
       <c r="O63">
-        <v>2799.96</v>
+        <v>599.97</v>
       </c>
     </row>
     <row r="64" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B64" t="str">
-        <v>TRX0177</v>
+        <v>TRX0118</v>
       </c>
       <c r="C64" s="13">
-        <v>45559</v>
+        <v>45705</v>
       </c>
       <c r="D64" t="str">
-        <v>CUST117</v>
+        <v>CUST212</v>
       </c>
       <c r="E64" t="str">
-        <v>Sandra Phillips</v>
+        <v>Richard Lee</v>
       </c>
       <c r="F64" t="str">
-        <v>P001</v>
+        <v>P008</v>
       </c>
       <c r="G64" t="str">
-        <v>Laptop</v>
+        <v>Bookshelf</v>
       </c>
       <c r="H64" t="str">
-        <v>Electronics</v>
+        <v>Furniture</v>
       </c>
       <c r="I64">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J64">
-        <v>899.99</v>
+        <v>149.99</v>
       </c>
       <c r="K64" t="str">
-        <v>Credit Card</v>
+        <v>Cash</v>
       </c>
       <c r="L64" t="str">
-        <v>North</v>
+        <v>South</v>
       </c>
       <c r="M64" t="str">
-        <v>Standard</v>
+        <v>Premium</v>
       </c>
       <c r="N64" s="13">
-        <v>45157</v>
+        <v>44728</v>
       </c>
       <c r="O64">
-        <v>2699.97</v>
+        <v>299.98</v>
       </c>
     </row>
     <row r="65" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B65" t="str">
-        <v>TRX0203</v>
+        <v>TRX0168</v>
       </c>
       <c r="C65" s="13">
-        <v>45572</v>
+        <v>45707</v>
       </c>
       <c r="D65" t="str">
-        <v>CUST123</v>
+        <v>CUST214</v>
       </c>
       <c r="E65" t="str">
-        <v>Sandra Phillips</v>
+        <v>Michael Brown</v>
       </c>
       <c r="F65" t="str">
-        <v>P003</v>
+        <v>P008</v>
       </c>
       <c r="G65" t="str">
-        <v>Headphones</v>
+        <v>Bookshelf</v>
       </c>
       <c r="H65" t="str">
-        <v>Electronics</v>
+        <v>Furniture</v>
       </c>
       <c r="I65">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J65">
         <v>149.99</v>
       </c>
       <c r="K65" t="str">
-        <v>Credit Card</v>
+        <v>PayPal</v>
       </c>
       <c r="L65" t="str">
-        <v>North</v>
+        <v>Central</v>
       </c>
       <c r="M65" t="str">
-        <v>Premium</v>
+        <v>Standard</v>
       </c>
       <c r="N65" s="13">
-        <v>45076</v>
+        <v>44633</v>
       </c>
       <c r="O65">
-        <v>599.96</v>
+        <v>449.97</v>
       </c>
     </row>
     <row r="66" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B66" t="str">
-        <v>TRX0055</v>
+        <v>TRX0221</v>
       </c>
       <c r="C66" s="13">
-        <v>45573</v>
+        <v>45708</v>
       </c>
       <c r="D66" t="str">
-        <v>CUST124</v>
+        <v>CUST216</v>
       </c>
       <c r="E66" t="str">
-        <v>Elizabeth Hall</v>
+        <v>Frank Torres</v>
       </c>
       <c r="F66" t="str">
-        <v>P002</v>
+        <v>P006</v>
       </c>
       <c r="G66" t="str">
-        <v>Smartphone</v>
+        <v>Office Chair</v>
       </c>
       <c r="H66" t="str">
-        <v>Electronics</v>
+        <v>Furniture</v>
       </c>
       <c r="I66">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J66">
-        <v>699.99</v>
+        <v>199.99</v>
       </c>
       <c r="K66" t="str">
-        <v>Debit Card</v>
+        <v>Cash</v>
       </c>
       <c r="L66" t="str">
-        <v>East</v>
+        <v>West</v>
       </c>
       <c r="M66" t="str">
         <v>Premium</v>
       </c>
       <c r="N66" s="13">
-        <v>45274</v>
+        <v>44823</v>
       </c>
       <c r="O66">
-        <v>1399.98</v>
+        <v>599.97</v>
       </c>
     </row>
     <row r="67" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B67" t="str">
-        <v>TRX0158</v>
+        <v>TRX0083</v>
       </c>
       <c r="C67" s="13">
-        <v>45579</v>
+        <v>45710</v>
       </c>
       <c r="D67" t="str">
-        <v>CUST127</v>
+        <v>CUST217</v>
       </c>
       <c r="E67" t="str">
-        <v>George Adams</v>
+        <v>Charles Allen</v>
       </c>
       <c r="F67" t="str">
-        <v>P001</v>
+        <v>P007</v>
       </c>
       <c r="G67" t="str">
-        <v>Laptop</v>
+        <v>Desk</v>
       </c>
       <c r="H67" t="str">
-        <v>Electronics</v>
+        <v>Furniture</v>
       </c>
       <c r="I67">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J67">
-        <v>899.99</v>
+        <v>299.99</v>
       </c>
       <c r="K67" t="str">
-        <v>PayPal</v>
+        <v>Cash</v>
       </c>
       <c r="L67" t="str">
         <v>West</v>
       </c>
       <c r="M67" t="str">
-        <v>Basic</v>
+        <v>Standard</v>
       </c>
       <c r="N67" s="13">
-        <v>45215</v>
+        <v>45142</v>
       </c>
       <c r="O67">
-        <v>2699.97</v>
+        <v>1499.95</v>
       </c>
     </row>
     <row r="68" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B68" t="str">
-        <v>TRX0173</v>
+        <v>TRX0200</v>
       </c>
       <c r="C68" s="13">
-        <v>45581</v>
+        <v>45711</v>
       </c>
       <c r="D68" t="str">
-        <v>CUST128</v>
+        <v>CUST220</v>
       </c>
       <c r="E68" t="str">
-        <v>Barbara Young</v>
+        <v>Arthur Edwards</v>
       </c>
       <c r="F68" t="str">
-        <v>P002</v>
+        <v>P008</v>
       </c>
       <c r="G68" t="str">
-        <v>Smartphone</v>
+        <v>Bookshelf</v>
       </c>
       <c r="H68" t="str">
-        <v>Electronics</v>
+        <v>Furniture</v>
       </c>
       <c r="I68">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J68">
-        <v>699.99</v>
+        <v>149.99</v>
       </c>
       <c r="K68" t="str">
-        <v>Cash</v>
+        <v>PayPal</v>
       </c>
       <c r="L68" t="str">
-        <v>East</v>
+        <v>North</v>
       </c>
       <c r="M68" t="str">
-        <v>Standard</v>
+        <v>Premium</v>
       </c>
       <c r="N68" s="13">
-        <v>45008</v>
+        <v>44412</v>
       </c>
       <c r="O68">
-        <v>3499.95</v>
+        <v>599.96</v>
       </c>
     </row>
     <row r="69" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B69" t="str">
-        <v>TRX0034</v>
+        <v>TRX0182</v>
       </c>
       <c r="C69" s="13">
-        <v>45581</v>
+        <v>45712</v>
       </c>
       <c r="D69" t="str">
-        <v>CUST129</v>
+        <v>CUST222</v>
       </c>
       <c r="E69" t="str">
-        <v>Raymond Ross</v>
+        <v>Steven Turner</v>
       </c>
       <c r="F69" t="str">
-        <v>P002</v>
+        <v>P006</v>
       </c>
       <c r="G69" t="str">
-        <v>Smartphone</v>
+        <v>Office Chair</v>
       </c>
       <c r="H69" t="str">
-        <v>Electronics</v>
+        <v>Furniture</v>
       </c>
       <c r="I69">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J69">
-        <v>699.99</v>
+        <v>199.99</v>
       </c>
       <c r="K69" t="str">
-        <v>Credit Card</v>
+        <v>Cash</v>
       </c>
       <c r="L69" t="str">
         <v>Central</v>
       </c>
       <c r="M69" t="str">
-        <v>Basic</v>
+        <v>Premium</v>
       </c>
       <c r="N69" s="13">
-        <v>45385</v>
+        <v>44573</v>
       </c>
       <c r="O69">
-        <v>2799.96</v>
+        <v>399.98</v>
       </c>
     </row>
     <row r="70" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B70" t="str">
-        <v>TRX0189</v>
+        <v>TRX0048</v>
       </c>
       <c r="C70" s="13">
-        <v>45581</v>
+        <v>45715</v>
       </c>
       <c r="D70" t="str">
-        <v>CUST130</v>
+        <v>CUST224</v>
       </c>
       <c r="E70" t="str">
-        <v>Sharon Butler</v>
+        <v>Virginia Sanders</v>
       </c>
       <c r="F70" t="str">
-        <v>P001</v>
+        <v>P007</v>
       </c>
       <c r="G70" t="str">
-        <v>Laptop</v>
+        <v>Desk</v>
       </c>
       <c r="H70" t="str">
-        <v>Electronics</v>
+        <v>Furniture</v>
       </c>
       <c r="I70">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J70">
-        <v>899.99</v>
+        <v>299.99</v>
       </c>
       <c r="K70" t="str">
-        <v>Credit Card</v>
+        <v>PayPal</v>
       </c>
       <c r="L70" t="str">
-        <v>East</v>
+        <v>South</v>
       </c>
       <c r="M70" t="str">
-        <v>Standard</v>
+        <v>Basic</v>
       </c>
       <c r="N70" s="13">
-        <v>45369</v>
+        <v>44576</v>
       </c>
       <c r="O70">
-        <v>899.99</v>
+        <v>599.98</v>
       </c>
     </row>
     <row r="71" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B71" t="str">
-        <v>TRX0190</v>
+        <v>TRX0227</v>
       </c>
       <c r="C71" s="13">
-        <v>45583</v>
+        <v>45718</v>
       </c>
       <c r="D71" t="str">
-        <v>CUST131</v>
+        <v>CUST225</v>
       </c>
       <c r="E71" t="str">
-        <v>Lawrence Reed</v>
+        <v>Charles Allen</v>
       </c>
       <c r="F71" t="str">
-        <v>P003</v>
+        <v>P008</v>
       </c>
       <c r="G71" t="str">
-        <v>Headphones</v>
+        <v>Bookshelf</v>
       </c>
       <c r="H71" t="str">
-        <v>Electronics</v>
+        <v>Furniture</v>
       </c>
       <c r="I71">
         <v>2</v>
@@ -66963,16 +66905,16 @@
         <v>149.99</v>
       </c>
       <c r="K71" t="str">
-        <v>Credit Card</v>
+        <v>Cash</v>
       </c>
       <c r="L71" t="str">
-        <v>West</v>
+        <v>Central</v>
       </c>
       <c r="M71" t="str">
         <v>Basic</v>
       </c>
       <c r="N71" s="13">
-        <v>44916</v>
+        <v>45068</v>
       </c>
       <c r="O71">
         <v>299.98</v>
@@ -66980,31 +66922,31 @@
     </row>
     <row r="72" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B72" t="str">
-        <v>TRX0079</v>
+        <v>TRX0186</v>
       </c>
       <c r="C72" s="13">
-        <v>45586</v>
+        <v>45724</v>
       </c>
       <c r="D72" t="str">
-        <v>CUST132</v>
+        <v>CUST230</v>
       </c>
       <c r="E72" t="str">
         <v>Lawrence Reed</v>
       </c>
       <c r="F72" t="str">
-        <v>P010</v>
+        <v>P008</v>
       </c>
       <c r="G72" t="str">
-        <v>Keyboard</v>
+        <v>Bookshelf</v>
       </c>
       <c r="H72" t="str">
-        <v>Electronics</v>
+        <v>Furniture</v>
       </c>
       <c r="I72">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J72">
-        <v>89.99</v>
+        <v>149.99</v>
       </c>
       <c r="K72" t="str">
         <v>PayPal</v>
@@ -67013,2653 +66955,233 @@
         <v>Central</v>
       </c>
       <c r="M72" t="str">
-        <v>Basic</v>
+        <v>Premium</v>
       </c>
       <c r="N72" s="13">
-        <v>44551</v>
+        <v>44632</v>
       </c>
       <c r="O72">
-        <v>269.97000000000003</v>
+        <v>299.98</v>
       </c>
     </row>
     <row r="73" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B73" t="str">
-        <v>TRX0095</v>
+        <v>TRX0199</v>
       </c>
       <c r="C73" s="13">
-        <v>45588</v>
+        <v>45724</v>
       </c>
       <c r="D73" t="str">
-        <v>CUST133</v>
+        <v>CUST232</v>
       </c>
       <c r="E73" t="str">
-        <v>Kathleen Bennett</v>
+        <v>Charles Allen</v>
       </c>
       <c r="F73" t="str">
-        <v>P003</v>
+        <v>P008</v>
       </c>
       <c r="G73" t="str">
-        <v>Headphones</v>
+        <v>Bookshelf</v>
       </c>
       <c r="H73" t="str">
-        <v>Electronics</v>
+        <v>Furniture</v>
       </c>
       <c r="I73">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J73">
         <v>149.99</v>
       </c>
       <c r="K73" t="str">
-        <v>PayPal</v>
+        <v>Cash</v>
       </c>
       <c r="L73" t="str">
         <v>Central</v>
       </c>
       <c r="M73" t="str">
-        <v>Basic</v>
+        <v>Standard</v>
       </c>
       <c r="N73" s="13">
-        <v>44473</v>
+        <v>45263</v>
       </c>
       <c r="O73">
-        <v>299.98</v>
+        <v>599.96</v>
       </c>
     </row>
     <row r="74" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B74" t="str">
-        <v>TRX0009</v>
+        <v>TRX0003</v>
       </c>
       <c r="C74" s="13">
-        <v>45588</v>
+        <v>45737</v>
       </c>
       <c r="D74" t="str">
-        <v>CUST134</v>
+        <v>CUST235</v>
       </c>
       <c r="E74" t="str">
-        <v>Sarah Davis</v>
+        <v>Emma Wilson</v>
       </c>
       <c r="F74" t="str">
-        <v>P002</v>
+        <v>P008</v>
       </c>
       <c r="G74" t="str">
-        <v>Smartphone</v>
+        <v>Bookshelf</v>
       </c>
       <c r="H74" t="str">
-        <v>Electronics</v>
+        <v>Furniture</v>
       </c>
       <c r="I74">
         <v>2</v>
       </c>
       <c r="J74">
-        <v>699.99</v>
+        <v>149.99</v>
       </c>
       <c r="K74" t="str">
         <v>Cash</v>
       </c>
       <c r="L74" t="str">
-        <v>Central</v>
+        <v>West</v>
       </c>
       <c r="M74" t="str">
-        <v>Basic</v>
+        <v>Premium</v>
       </c>
       <c r="N74" s="13">
-        <v>44992</v>
+        <v>45233</v>
       </c>
       <c r="O74">
-        <v>1399.98</v>
+        <v>299.98</v>
       </c>
     </row>
     <row r="75" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B75" t="str">
-        <v>TRX0167</v>
+        <v>TRX0019</v>
       </c>
       <c r="C75" s="13">
-        <v>45589</v>
+        <v>45739</v>
       </c>
       <c r="D75" t="str">
-        <v>CUST135</v>
+        <v>CUST238</v>
       </c>
       <c r="E75" t="str">
-        <v>Betty Campbell</v>
+        <v>Paul Baker</v>
       </c>
       <c r="F75" t="str">
-        <v>P002</v>
+        <v>P007</v>
       </c>
       <c r="G75" t="str">
-        <v>Smartphone</v>
+        <v>Desk</v>
       </c>
       <c r="H75" t="str">
-        <v>Electronics</v>
+        <v>Furniture</v>
       </c>
       <c r="I75">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J75">
-        <v>699.99</v>
+        <v>299.99</v>
       </c>
       <c r="K75" t="str">
-        <v>Cash</v>
+        <v>Credit Card</v>
       </c>
       <c r="L75" t="str">
-        <v>North</v>
+        <v>West</v>
       </c>
       <c r="M75" t="str">
         <v>Premium</v>
       </c>
       <c r="N75" s="13">
-        <v>44635</v>
+        <v>45234</v>
       </c>
       <c r="O75">
-        <v>3499.95</v>
+        <v>899.97</v>
       </c>
     </row>
     <row r="76" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B76" t="str">
-        <v>TRX0153</v>
+        <v>TRX0050</v>
       </c>
       <c r="C76" s="13">
-        <v>45592</v>
+        <v>45740</v>
       </c>
       <c r="D76" t="str">
-        <v>CUST136</v>
+        <v>CUST239</v>
       </c>
       <c r="E76" t="str">
-        <v>Raymond Ross</v>
+        <v>John Smith</v>
       </c>
       <c r="F76" t="str">
-        <v>P010</v>
+        <v>P008</v>
       </c>
       <c r="G76" t="str">
-        <v>Keyboard</v>
+        <v>Bookshelf</v>
       </c>
       <c r="H76" t="str">
-        <v>Electronics</v>
+        <v>Furniture</v>
       </c>
       <c r="I76">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J76">
-        <v>89.99</v>
+        <v>149.99</v>
       </c>
       <c r="K76" t="str">
-        <v>Credit Card</v>
+        <v>PayPal</v>
       </c>
       <c r="L76" t="str">
-        <v>North</v>
+        <v>West</v>
       </c>
       <c r="M76" t="str">
         <v>Standard</v>
       </c>
       <c r="N76" s="13">
-        <v>44615</v>
+        <v>44560</v>
       </c>
       <c r="O76">
-        <v>269.97000000000003</v>
+        <v>599.96</v>
       </c>
     </row>
     <row r="77" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B77" t="str">
-        <v>TRX0057</v>
+        <v>TRX0197</v>
       </c>
       <c r="C77" s="13">
-        <v>45597</v>
+        <v>45746</v>
       </c>
       <c r="D77" t="str">
-        <v>CUST137</v>
+        <v>CUST242</v>
       </c>
       <c r="E77" t="str">
-        <v>Paul Baker</v>
+        <v>Virginia Sanders</v>
       </c>
       <c r="F77" t="str">
-        <v>P009</v>
+        <v>P008</v>
       </c>
       <c r="G77" t="str">
-        <v>Monitor</v>
+        <v>Bookshelf</v>
       </c>
       <c r="H77" t="str">
-        <v>Electronics</v>
+        <v>Furniture</v>
       </c>
       <c r="I77">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J77">
-        <v>249.99</v>
+        <v>149.99</v>
       </c>
       <c r="K77" t="str">
-        <v>Credit Card</v>
+        <v>PayPal</v>
       </c>
       <c r="L77" t="str">
-        <v>South</v>
+        <v>Central</v>
       </c>
       <c r="M77" t="str">
         <v>Standard</v>
       </c>
       <c r="N77" s="13">
-        <v>44881</v>
+        <v>45171</v>
       </c>
       <c r="O77">
-        <v>1249.95</v>
-      </c>
-    </row>
-    <row r="78" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B78" t="str">
-        <v>TRX0060</v>
-      </c>
-      <c r="C78" s="13">
-        <v>45603</v>
-      </c>
-      <c r="D78" t="str">
-        <v>CUST139</v>
-      </c>
-      <c r="E78" t="str">
-        <v>Patricia Moore</v>
-      </c>
-      <c r="F78" t="str">
-        <v>P010</v>
-      </c>
-      <c r="G78" t="str">
-        <v>Keyboard</v>
-      </c>
-      <c r="H78" t="str">
-        <v>Electronics</v>
-      </c>
-      <c r="I78">
-        <v>3</v>
-      </c>
-      <c r="J78">
-        <v>89.99</v>
-      </c>
-      <c r="K78" t="str">
-        <v>Credit Card</v>
-      </c>
-      <c r="L78" t="str">
-        <v>North</v>
-      </c>
-      <c r="M78" t="str">
-        <v>Premium</v>
-      </c>
-      <c r="N78" s="13">
-        <v>44420</v>
-      </c>
-      <c r="O78">
-        <v>269.97000000000003</v>
-      </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B79" t="str">
-        <v>TRX0090</v>
-      </c>
-      <c r="C79" s="13">
-        <v>45605</v>
-      </c>
-      <c r="D79" t="str">
-        <v>CUST141</v>
-      </c>
-      <c r="E79" t="str">
-        <v>Margaret Wright</v>
-      </c>
-      <c r="F79" t="str">
-        <v>P009</v>
-      </c>
-      <c r="G79" t="str">
-        <v>Monitor</v>
-      </c>
-      <c r="H79" t="str">
-        <v>Electronics</v>
-      </c>
-      <c r="I79">
-        <v>1</v>
-      </c>
-      <c r="J79">
-        <v>249.99</v>
-      </c>
-      <c r="K79" t="str">
-        <v>Credit Card</v>
-      </c>
-      <c r="L79" t="str">
-        <v>North</v>
-      </c>
-      <c r="M79" t="str">
-        <v>Premium</v>
-      </c>
-      <c r="N79" s="13">
-        <v>44828</v>
-      </c>
-      <c r="O79">
-        <v>249.99</v>
-      </c>
-    </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B80" t="str">
-        <v>TRX0035</v>
-      </c>
-      <c r="C80" s="13">
-        <v>45607</v>
-      </c>
-      <c r="D80" t="str">
-        <v>CUST142</v>
-      </c>
-      <c r="E80" t="str">
-        <v>Peter Richardson</v>
-      </c>
-      <c r="F80" t="str">
-        <v>P003</v>
-      </c>
-      <c r="G80" t="str">
-        <v>Headphones</v>
-      </c>
-      <c r="H80" t="str">
-        <v>Electronics</v>
-      </c>
-      <c r="I80">
-        <v>3</v>
-      </c>
-      <c r="J80">
-        <v>149.99</v>
-      </c>
-      <c r="K80" t="str">
-        <v>Cash</v>
-      </c>
-      <c r="L80" t="str">
-        <v>North</v>
-      </c>
-      <c r="M80" t="str">
-        <v>Basic</v>
-      </c>
-      <c r="N80" s="13">
-        <v>44769</v>
-      </c>
-      <c r="O80">
         <v>449.97</v>
-      </c>
-    </row>
-    <row r="81" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B81" t="str">
-        <v>TRX0076</v>
-      </c>
-      <c r="C81" s="13">
-        <v>45607</v>
-      </c>
-      <c r="D81" t="str">
-        <v>CUST144</v>
-      </c>
-      <c r="E81" t="str">
-        <v>Patricia Moore</v>
-      </c>
-      <c r="F81" t="str">
-        <v>P009</v>
-      </c>
-      <c r="G81" t="str">
-        <v>Monitor</v>
-      </c>
-      <c r="H81" t="str">
-        <v>Electronics</v>
-      </c>
-      <c r="I81">
-        <v>4</v>
-      </c>
-      <c r="J81">
-        <v>249.99</v>
-      </c>
-      <c r="K81" t="str">
-        <v>Credit Card</v>
-      </c>
-      <c r="L81" t="str">
-        <v>West</v>
-      </c>
-      <c r="M81" t="str">
-        <v>Standard</v>
-      </c>
-      <c r="N81" s="13">
-        <v>44659</v>
-      </c>
-      <c r="O81">
-        <v>999.96</v>
-      </c>
-    </row>
-    <row r="82" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B82" t="str">
-        <v>TRX0033</v>
-      </c>
-      <c r="C82" s="13">
-        <v>45613</v>
-      </c>
-      <c r="D82" t="str">
-        <v>CUST148</v>
-      </c>
-      <c r="E82" t="str">
-        <v>Mark Carter</v>
-      </c>
-      <c r="F82" t="str">
-        <v>P002</v>
-      </c>
-      <c r="G82" t="str">
-        <v>Smartphone</v>
-      </c>
-      <c r="H82" t="str">
-        <v>Electronics</v>
-      </c>
-      <c r="I82">
-        <v>2</v>
-      </c>
-      <c r="J82">
-        <v>699.99</v>
-      </c>
-      <c r="K82" t="str">
-        <v>PayPal</v>
-      </c>
-      <c r="L82" t="str">
-        <v>West</v>
-      </c>
-      <c r="M82" t="str">
-        <v>Standard</v>
-      </c>
-      <c r="N82" s="13">
-        <v>44770</v>
-      </c>
-      <c r="O82">
-        <v>1399.98</v>
-      </c>
-    </row>
-    <row r="83" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B83" t="str">
-        <v>TRX0148</v>
-      </c>
-      <c r="C83" s="13">
-        <v>45619</v>
-      </c>
-      <c r="D83" t="str">
-        <v>CUST151</v>
-      </c>
-      <c r="E83" t="str">
-        <v>Sarah Davis</v>
-      </c>
-      <c r="F83" t="str">
-        <v>P002</v>
-      </c>
-      <c r="G83" t="str">
-        <v>Smartphone</v>
-      </c>
-      <c r="H83" t="str">
-        <v>Electronics</v>
-      </c>
-      <c r="I83">
-        <v>3</v>
-      </c>
-      <c r="J83">
-        <v>699.99</v>
-      </c>
-      <c r="K83" t="str">
-        <v>PayPal</v>
-      </c>
-      <c r="L83" t="str">
-        <v>West</v>
-      </c>
-      <c r="M83" t="str">
-        <v>Standard</v>
-      </c>
-      <c r="N83" s="13">
-        <v>44583</v>
-      </c>
-      <c r="O83">
-        <v>2099.9699999999998</v>
-      </c>
-    </row>
-    <row r="84" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B84" t="str">
-        <v>TRX0012</v>
-      </c>
-      <c r="C84" s="13">
-        <v>45622</v>
-      </c>
-      <c r="D84" t="str">
-        <v>CUST152</v>
-      </c>
-      <c r="E84" t="str">
-        <v>Douglas Watson</v>
-      </c>
-      <c r="F84" t="str">
-        <v>P009</v>
-      </c>
-      <c r="G84" t="str">
-        <v>Monitor</v>
-      </c>
-      <c r="H84" t="str">
-        <v>Electronics</v>
-      </c>
-      <c r="I84">
-        <v>5</v>
-      </c>
-      <c r="J84">
-        <v>249.99</v>
-      </c>
-      <c r="K84" t="str">
-        <v>Credit Card</v>
-      </c>
-      <c r="L84" t="str">
-        <v>North</v>
-      </c>
-      <c r="M84" t="str">
-        <v>Basic</v>
-      </c>
-      <c r="N84" s="13">
-        <v>44873</v>
-      </c>
-      <c r="O84">
-        <v>1249.95</v>
-      </c>
-    </row>
-    <row r="85" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B85" t="str">
-        <v>TRX0094</v>
-      </c>
-      <c r="C85" s="13">
-        <v>45627</v>
-      </c>
-      <c r="D85" t="str">
-        <v>CUST155</v>
-      </c>
-      <c r="E85" t="str">
-        <v>Charles Allen</v>
-      </c>
-      <c r="F85" t="str">
-        <v>P009</v>
-      </c>
-      <c r="G85" t="str">
-        <v>Monitor</v>
-      </c>
-      <c r="H85" t="str">
-        <v>Electronics</v>
-      </c>
-      <c r="I85">
-        <v>5</v>
-      </c>
-      <c r="J85">
-        <v>249.99</v>
-      </c>
-      <c r="K85" t="str">
-        <v>Cash</v>
-      </c>
-      <c r="L85" t="str">
-        <v>Central</v>
-      </c>
-      <c r="M85" t="str">
-        <v>Premium</v>
-      </c>
-      <c r="N85" s="13">
-        <v>44485</v>
-      </c>
-      <c r="O85">
-        <v>1249.95</v>
-      </c>
-    </row>
-    <row r="86" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B86" t="str">
-        <v>TRX0133</v>
-      </c>
-      <c r="C86" s="13">
-        <v>45627</v>
-      </c>
-      <c r="D86" t="str">
-        <v>CUST156</v>
-      </c>
-      <c r="E86" t="str">
-        <v>Joseph Jackson</v>
-      </c>
-      <c r="F86" t="str">
-        <v>P003</v>
-      </c>
-      <c r="G86" t="str">
-        <v>Headphones</v>
-      </c>
-      <c r="H86" t="str">
-        <v>Electronics</v>
-      </c>
-      <c r="I86">
-        <v>2</v>
-      </c>
-      <c r="J86">
-        <v>149.99</v>
-      </c>
-      <c r="K86" t="str">
-        <v>Cash</v>
-      </c>
-      <c r="L86" t="str">
-        <v>South</v>
-      </c>
-      <c r="M86" t="str">
-        <v>Premium</v>
-      </c>
-      <c r="N86" s="13">
-        <v>44475</v>
-      </c>
-      <c r="O86">
-        <v>299.98</v>
-      </c>
-    </row>
-    <row r="87" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B87" t="str">
-        <v>TRX0201</v>
-      </c>
-      <c r="C87" s="13">
-        <v>45627</v>
-      </c>
-      <c r="D87" t="str">
-        <v>CUST157</v>
-      </c>
-      <c r="E87" t="str">
-        <v>Mark Carter</v>
-      </c>
-      <c r="F87" t="str">
-        <v>P002</v>
-      </c>
-      <c r="G87" t="str">
-        <v>Smartphone</v>
-      </c>
-      <c r="H87" t="str">
-        <v>Electronics</v>
-      </c>
-      <c r="I87">
-        <v>5</v>
-      </c>
-      <c r="J87">
-        <v>699.99</v>
-      </c>
-      <c r="K87" t="str">
-        <v>Debit Card</v>
-      </c>
-      <c r="L87" t="str">
-        <v>West</v>
-      </c>
-      <c r="M87" t="str">
-        <v>Standard</v>
-      </c>
-      <c r="N87" s="13">
-        <v>44944</v>
-      </c>
-      <c r="O87">
-        <v>3499.95</v>
-      </c>
-    </row>
-    <row r="88" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B88" t="str">
-        <v>TRX0137</v>
-      </c>
-      <c r="C88" s="13">
-        <v>45629</v>
-      </c>
-      <c r="D88" t="str">
-        <v>CUST158</v>
-      </c>
-      <c r="E88" t="str">
-        <v>William White</v>
-      </c>
-      <c r="F88" t="str">
-        <v>P009</v>
-      </c>
-      <c r="G88" t="str">
-        <v>Monitor</v>
-      </c>
-      <c r="H88" t="str">
-        <v>Electronics</v>
-      </c>
-      <c r="I88">
-        <v>4</v>
-      </c>
-      <c r="J88">
-        <v>249.99</v>
-      </c>
-      <c r="K88" t="str">
-        <v>PayPal</v>
-      </c>
-      <c r="L88" t="str">
-        <v>East</v>
-      </c>
-      <c r="M88" t="str">
-        <v>Premium</v>
-      </c>
-      <c r="N88" s="13">
-        <v>45098</v>
-      </c>
-      <c r="O88">
-        <v>999.96</v>
-      </c>
-    </row>
-    <row r="89" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B89" t="str">
-        <v>TRX0066</v>
-      </c>
-      <c r="C89" s="13">
-        <v>45630</v>
-      </c>
-      <c r="D89" t="str">
-        <v>CUST159</v>
-      </c>
-      <c r="E89" t="str">
-        <v>Dorothy Nelson</v>
-      </c>
-      <c r="F89" t="str">
-        <v>P002</v>
-      </c>
-      <c r="G89" t="str">
-        <v>Smartphone</v>
-      </c>
-      <c r="H89" t="str">
-        <v>Electronics</v>
-      </c>
-      <c r="I89">
-        <v>4</v>
-      </c>
-      <c r="J89">
-        <v>699.99</v>
-      </c>
-      <c r="K89" t="str">
-        <v>Credit Card</v>
-      </c>
-      <c r="L89" t="str">
-        <v>North</v>
-      </c>
-      <c r="M89" t="str">
-        <v>Premium</v>
-      </c>
-      <c r="N89" s="13">
-        <v>44703</v>
-      </c>
-      <c r="O89">
-        <v>2799.96</v>
-      </c>
-    </row>
-    <row r="90" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B90" t="str">
-        <v>TRX0180</v>
-      </c>
-      <c r="C90" s="13">
-        <v>45635</v>
-      </c>
-      <c r="D90" t="str">
-        <v>CUST160</v>
-      </c>
-      <c r="E90" t="str">
-        <v>Nancy Collins</v>
-      </c>
-      <c r="F90" t="str">
-        <v>P009</v>
-      </c>
-      <c r="G90" t="str">
-        <v>Monitor</v>
-      </c>
-      <c r="H90" t="str">
-        <v>Electronics</v>
-      </c>
-      <c r="I90">
-        <v>2</v>
-      </c>
-      <c r="J90">
-        <v>249.99</v>
-      </c>
-      <c r="K90" t="str">
-        <v>Credit Card</v>
-      </c>
-      <c r="L90" t="str">
-        <v>Central</v>
-      </c>
-      <c r="M90" t="str">
-        <v>Premium</v>
-      </c>
-      <c r="N90" s="13">
-        <v>44396</v>
-      </c>
-      <c r="O90">
-        <v>499.98</v>
-      </c>
-    </row>
-    <row r="91" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B91" t="str">
-        <v>TRX0032</v>
-      </c>
-      <c r="C91" s="13">
-        <v>45638</v>
-      </c>
-      <c r="D91" t="str">
-        <v>CUST164</v>
-      </c>
-      <c r="E91" t="str">
-        <v>Peter Richardson</v>
-      </c>
-      <c r="F91" t="str">
-        <v>P001</v>
-      </c>
-      <c r="G91" t="str">
-        <v>Laptop</v>
-      </c>
-      <c r="H91" t="str">
-        <v>Electronics</v>
-      </c>
-      <c r="I91">
-        <v>2</v>
-      </c>
-      <c r="J91">
-        <v>899.99</v>
-      </c>
-      <c r="K91" t="str">
-        <v>Cash</v>
-      </c>
-      <c r="L91" t="str">
-        <v>North</v>
-      </c>
-      <c r="M91" t="str">
-        <v>Basic</v>
-      </c>
-      <c r="N91" s="13">
-        <v>44406</v>
-      </c>
-      <c r="O91">
-        <v>1799.98</v>
-      </c>
-    </row>
-    <row r="92" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B92" t="str">
-        <v>TRX0183</v>
-      </c>
-      <c r="C92" s="13">
-        <v>45645</v>
-      </c>
-      <c r="D92" t="str">
-        <v>CUST168</v>
-      </c>
-      <c r="E92" t="str">
-        <v>David Martinez</v>
-      </c>
-      <c r="F92" t="str">
-        <v>P010</v>
-      </c>
-      <c r="G92" t="str">
-        <v>Keyboard</v>
-      </c>
-      <c r="H92" t="str">
-        <v>Electronics</v>
-      </c>
-      <c r="I92">
-        <v>1</v>
-      </c>
-      <c r="J92">
-        <v>89.99</v>
-      </c>
-      <c r="K92" t="str">
-        <v>Debit Card</v>
-      </c>
-      <c r="L92" t="str">
-        <v>Central</v>
-      </c>
-      <c r="M92" t="str">
-        <v>Standard</v>
-      </c>
-      <c r="N92" s="13">
-        <v>44760</v>
-      </c>
-      <c r="O92">
-        <v>89.99</v>
-      </c>
-    </row>
-    <row r="93" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B93" t="str">
-        <v>TRX0163</v>
-      </c>
-      <c r="C93" s="13">
-        <v>45645</v>
-      </c>
-      <c r="D93" t="str">
-        <v>CUST169</v>
-      </c>
-      <c r="E93" t="str">
-        <v>Daniel King</v>
-      </c>
-      <c r="F93" t="str">
-        <v>P001</v>
-      </c>
-      <c r="G93" t="str">
-        <v>Laptop</v>
-      </c>
-      <c r="H93" t="str">
-        <v>Electronics</v>
-      </c>
-      <c r="I93">
-        <v>5</v>
-      </c>
-      <c r="J93">
-        <v>899.99</v>
-      </c>
-      <c r="K93" t="str">
-        <v>Debit Card</v>
-      </c>
-      <c r="L93" t="str">
-        <v>East</v>
-      </c>
-      <c r="M93" t="str">
-        <v>Standard</v>
-      </c>
-      <c r="N93" s="13">
-        <v>44625</v>
-      </c>
-      <c r="O93">
-        <v>4499.95</v>
-      </c>
-    </row>
-    <row r="94" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B94" t="str">
-        <v>TRX0164</v>
-      </c>
-      <c r="C94" s="13">
-        <v>45648</v>
-      </c>
-      <c r="D94" t="str">
-        <v>CUST171</v>
-      </c>
-      <c r="E94" t="str">
-        <v>Linda Martin</v>
-      </c>
-      <c r="F94" t="str">
-        <v>P003</v>
-      </c>
-      <c r="G94" t="str">
-        <v>Headphones</v>
-      </c>
-      <c r="H94" t="str">
-        <v>Electronics</v>
-      </c>
-      <c r="I94">
-        <v>2</v>
-      </c>
-      <c r="J94">
-        <v>149.99</v>
-      </c>
-      <c r="K94" t="str">
-        <v>Debit Card</v>
-      </c>
-      <c r="L94" t="str">
-        <v>West</v>
-      </c>
-      <c r="M94" t="str">
-        <v>Premium</v>
-      </c>
-      <c r="N94" s="13">
-        <v>45280</v>
-      </c>
-      <c r="O94">
-        <v>299.98</v>
-      </c>
-    </row>
-    <row r="95" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B95" t="str">
-        <v>TRX0156</v>
-      </c>
-      <c r="C95" s="13">
-        <v>45655</v>
-      </c>
-      <c r="D95" t="str">
-        <v>CUST176</v>
-      </c>
-      <c r="E95" t="str">
-        <v>Robert Thomas</v>
-      </c>
-      <c r="F95" t="str">
-        <v>P010</v>
-      </c>
-      <c r="G95" t="str">
-        <v>Keyboard</v>
-      </c>
-      <c r="H95" t="str">
-        <v>Electronics</v>
-      </c>
-      <c r="I95">
-        <v>1</v>
-      </c>
-      <c r="J95">
-        <v>89.99</v>
-      </c>
-      <c r="K95" t="str">
-        <v>Credit Card</v>
-      </c>
-      <c r="L95" t="str">
-        <v>South</v>
-      </c>
-      <c r="M95" t="str">
-        <v>Premium</v>
-      </c>
-      <c r="N95" s="13">
-        <v>44591</v>
-      </c>
-      <c r="O95">
-        <v>89.99</v>
-      </c>
-    </row>
-    <row r="96" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B96" t="str">
-        <v>TRX0207</v>
-      </c>
-      <c r="C96" s="13">
-        <v>45657</v>
-      </c>
-      <c r="D96" t="str">
-        <v>CUST178</v>
-      </c>
-      <c r="E96" t="str">
-        <v>Mark Carter</v>
-      </c>
-      <c r="F96" t="str">
-        <v>P001</v>
-      </c>
-      <c r="G96" t="str">
-        <v>Laptop</v>
-      </c>
-      <c r="H96" t="str">
-        <v>Electronics</v>
-      </c>
-      <c r="I96">
-        <v>1</v>
-      </c>
-      <c r="J96">
-        <v>899.99</v>
-      </c>
-      <c r="K96" t="str">
-        <v>PayPal</v>
-      </c>
-      <c r="L96" t="str">
-        <v>North</v>
-      </c>
-      <c r="M96" t="str">
-        <v>Premium</v>
-      </c>
-      <c r="N96" s="13">
-        <v>45050</v>
-      </c>
-      <c r="O96">
-        <v>899.99</v>
-      </c>
-    </row>
-    <row r="97" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B97" t="str">
-        <v>TRX0056</v>
-      </c>
-      <c r="C97" s="13">
-        <v>45660</v>
-      </c>
-      <c r="D97" t="str">
-        <v>CUST179</v>
-      </c>
-      <c r="E97" t="str">
-        <v>Daniel King</v>
-      </c>
-      <c r="F97" t="str">
-        <v>P010</v>
-      </c>
-      <c r="G97" t="str">
-        <v>Keyboard</v>
-      </c>
-      <c r="H97" t="str">
-        <v>Electronics</v>
-      </c>
-      <c r="I97">
-        <v>2</v>
-      </c>
-      <c r="J97">
-        <v>89.99</v>
-      </c>
-      <c r="K97" t="str">
-        <v>Credit Card</v>
-      </c>
-      <c r="L97" t="str">
-        <v>South</v>
-      </c>
-      <c r="M97" t="str">
-        <v>Premium</v>
-      </c>
-      <c r="N97" s="13">
-        <v>44564</v>
-      </c>
-      <c r="O97">
-        <v>179.98</v>
-      </c>
-    </row>
-    <row r="98" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B98" t="str">
-        <v>TRX0026</v>
-      </c>
-      <c r="C98" s="13">
-        <v>45661</v>
-      </c>
-      <c r="D98" t="str">
-        <v>CUST180</v>
-      </c>
-      <c r="E98" t="str">
-        <v>Arthur Edwards</v>
-      </c>
-      <c r="F98" t="str">
-        <v>P001</v>
-      </c>
-      <c r="G98" t="str">
-        <v>Laptop</v>
-      </c>
-      <c r="H98" t="str">
-        <v>Electronics</v>
-      </c>
-      <c r="I98">
-        <v>1</v>
-      </c>
-      <c r="J98">
-        <v>899.99</v>
-      </c>
-      <c r="K98" t="str">
-        <v>PayPal</v>
-      </c>
-      <c r="L98" t="str">
-        <v>North</v>
-      </c>
-      <c r="M98" t="str">
-        <v>Standard</v>
-      </c>
-      <c r="N98" s="13">
-        <v>44752</v>
-      </c>
-      <c r="O98">
-        <v>899.99</v>
-      </c>
-    </row>
-    <row r="99" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B99" t="str">
-        <v>TRX0237</v>
-      </c>
-      <c r="C99" s="13">
-        <v>45663</v>
-      </c>
-      <c r="D99" t="str">
-        <v>CUST181</v>
-      </c>
-      <c r="E99" t="str">
-        <v>Lisa Anderson</v>
-      </c>
-      <c r="F99" t="str">
-        <v>P003</v>
-      </c>
-      <c r="G99" t="str">
-        <v>Headphones</v>
-      </c>
-      <c r="H99" t="str">
-        <v>Electronics</v>
-      </c>
-      <c r="I99">
-        <v>5</v>
-      </c>
-      <c r="J99">
-        <v>149.99</v>
-      </c>
-      <c r="K99" t="str">
-        <v>PayPal</v>
-      </c>
-      <c r="L99" t="str">
-        <v>East</v>
-      </c>
-      <c r="M99" t="str">
-        <v>Premium</v>
-      </c>
-      <c r="N99" s="13">
-        <v>44824</v>
-      </c>
-      <c r="O99">
-        <v>749.95</v>
-      </c>
-    </row>
-    <row r="100" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B100" t="str">
-        <v>TRX0125</v>
-      </c>
-      <c r="C100" s="13">
-        <v>45666</v>
-      </c>
-      <c r="D100" t="str">
-        <v>CUST183</v>
-      </c>
-      <c r="E100" t="str">
-        <v>Karen Hill</v>
-      </c>
-      <c r="F100" t="str">
-        <v>P002</v>
-      </c>
-      <c r="G100" t="str">
-        <v>Smartphone</v>
-      </c>
-      <c r="H100" t="str">
-        <v>Electronics</v>
-      </c>
-      <c r="I100">
-        <v>3</v>
-      </c>
-      <c r="J100">
-        <v>699.99</v>
-      </c>
-      <c r="K100" t="str">
-        <v>Credit Card</v>
-      </c>
-      <c r="L100" t="str">
-        <v>Central</v>
-      </c>
-      <c r="M100" t="str">
-        <v>Premium</v>
-      </c>
-      <c r="N100" s="13">
-        <v>45105</v>
-      </c>
-      <c r="O100">
-        <v>2099.9699999999998</v>
-      </c>
-    </row>
-    <row r="101" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B101" t="str">
-        <v>TRX0243</v>
-      </c>
-      <c r="C101" s="13">
-        <v>45667</v>
-      </c>
-      <c r="D101" t="str">
-        <v>CUST185</v>
-      </c>
-      <c r="E101" t="str">
-        <v>Virginia Sanders</v>
-      </c>
-      <c r="F101" t="str">
-        <v>P009</v>
-      </c>
-      <c r="G101" t="str">
-        <v>Monitor</v>
-      </c>
-      <c r="H101" t="str">
-        <v>Electronics</v>
-      </c>
-      <c r="I101">
-        <v>5</v>
-      </c>
-      <c r="J101">
-        <v>249.99</v>
-      </c>
-      <c r="K101" t="str">
-        <v>Credit Card</v>
-      </c>
-      <c r="L101" t="str">
-        <v>South</v>
-      </c>
-      <c r="M101" t="str">
-        <v>Basic</v>
-      </c>
-      <c r="N101" s="13">
-        <v>45330</v>
-      </c>
-      <c r="O101">
-        <v>1249.95</v>
-      </c>
-    </row>
-    <row r="102" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B102" t="str">
-        <v>TRX0084</v>
-      </c>
-      <c r="C102" s="13">
-        <v>45668</v>
-      </c>
-      <c r="D102" t="str">
-        <v>CUST186</v>
-      </c>
-      <c r="E102" t="str">
-        <v>Steven Turner</v>
-      </c>
-      <c r="F102" t="str">
-        <v>P003</v>
-      </c>
-      <c r="G102" t="str">
-        <v>Headphones</v>
-      </c>
-      <c r="H102" t="str">
-        <v>Electronics</v>
-      </c>
-      <c r="I102">
-        <v>4</v>
-      </c>
-      <c r="J102">
-        <v>149.99</v>
-      </c>
-      <c r="K102" t="str">
-        <v>Debit Card</v>
-      </c>
-      <c r="L102" t="str">
-        <v>East</v>
-      </c>
-      <c r="M102" t="str">
-        <v>Standard</v>
-      </c>
-      <c r="N102" s="13">
-        <v>44536</v>
-      </c>
-      <c r="O102">
-        <v>599.96</v>
-      </c>
-    </row>
-    <row r="103" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B103" t="str">
-        <v>TRX0238</v>
-      </c>
-      <c r="C103" s="13">
-        <v>45668</v>
-      </c>
-      <c r="D103" t="str">
-        <v>CUST187</v>
-      </c>
-      <c r="E103" t="str">
-        <v>Michelle Rogers</v>
-      </c>
-      <c r="F103" t="str">
-        <v>P002</v>
-      </c>
-      <c r="G103" t="str">
-        <v>Smartphone</v>
-      </c>
-      <c r="H103" t="str">
-        <v>Electronics</v>
-      </c>
-      <c r="I103">
-        <v>3</v>
-      </c>
-      <c r="J103">
-        <v>699.99</v>
-      </c>
-      <c r="K103" t="str">
-        <v>Cash</v>
-      </c>
-      <c r="L103" t="str">
-        <v>North</v>
-      </c>
-      <c r="M103" t="str">
-        <v>Premium</v>
-      </c>
-      <c r="N103" s="13">
-        <v>44602</v>
-      </c>
-      <c r="O103">
-        <v>2099.9699999999998</v>
-      </c>
-    </row>
-    <row r="104" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B104" t="str">
-        <v>TRX0087</v>
-      </c>
-      <c r="C104" s="13">
-        <v>45671</v>
-      </c>
-      <c r="D104" t="str">
-        <v>CUST190</v>
-      </c>
-      <c r="E104" t="str">
-        <v>Betty Campbell</v>
-      </c>
-      <c r="F104" t="str">
-        <v>P009</v>
-      </c>
-      <c r="G104" t="str">
-        <v>Monitor</v>
-      </c>
-      <c r="H104" t="str">
-        <v>Electronics</v>
-      </c>
-      <c r="I104">
-        <v>4</v>
-      </c>
-      <c r="J104">
-        <v>249.99</v>
-      </c>
-      <c r="K104" t="str">
-        <v>Credit Card</v>
-      </c>
-      <c r="L104" t="str">
-        <v>North</v>
-      </c>
-      <c r="M104" t="str">
-        <v>Premium</v>
-      </c>
-      <c r="N104" s="13">
-        <v>44460</v>
-      </c>
-      <c r="O104">
-        <v>999.96</v>
-      </c>
-    </row>
-    <row r="105" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B105" t="str">
-        <v>TRX0107</v>
-      </c>
-      <c r="C105" s="13">
-        <v>45671</v>
-      </c>
-      <c r="D105" t="str">
-        <v>CUST191</v>
-      </c>
-      <c r="E105" t="str">
-        <v>Helen Roberts</v>
-      </c>
-      <c r="F105" t="str">
-        <v>P003</v>
-      </c>
-      <c r="G105" t="str">
-        <v>Headphones</v>
-      </c>
-      <c r="H105" t="str">
-        <v>Electronics</v>
-      </c>
-      <c r="I105">
-        <v>2</v>
-      </c>
-      <c r="J105">
-        <v>149.99</v>
-      </c>
-      <c r="K105" t="str">
-        <v>Cash</v>
-      </c>
-      <c r="L105" t="str">
-        <v>North</v>
-      </c>
-      <c r="M105" t="str">
-        <v>Standard</v>
-      </c>
-      <c r="N105" s="13">
-        <v>44913</v>
-      </c>
-      <c r="O105">
-        <v>299.98</v>
-      </c>
-    </row>
-    <row r="106" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B106" t="str">
-        <v>TRX0159</v>
-      </c>
-      <c r="C106" s="13">
-        <v>45683</v>
-      </c>
-      <c r="D106" t="str">
-        <v>CUST198</v>
-      </c>
-      <c r="E106" t="str">
-        <v>Dorothy Nelson</v>
-      </c>
-      <c r="F106" t="str">
-        <v>P009</v>
-      </c>
-      <c r="G106" t="str">
-        <v>Monitor</v>
-      </c>
-      <c r="H106" t="str">
-        <v>Electronics</v>
-      </c>
-      <c r="I106">
-        <v>4</v>
-      </c>
-      <c r="J106">
-        <v>249.99</v>
-      </c>
-      <c r="K106" t="str">
-        <v>Debit Card</v>
-      </c>
-      <c r="L106" t="str">
-        <v>Central</v>
-      </c>
-      <c r="M106" t="str">
-        <v>Premium</v>
-      </c>
-      <c r="N106" s="13">
-        <v>45217</v>
-      </c>
-      <c r="O106">
-        <v>999.96</v>
-      </c>
-    </row>
-    <row r="107" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B107" t="str">
-        <v>TRX0030</v>
-      </c>
-      <c r="C107" s="13">
-        <v>45686</v>
-      </c>
-      <c r="D107" t="str">
-        <v>CUST199</v>
-      </c>
-      <c r="E107" t="str">
-        <v>William White</v>
-      </c>
-      <c r="F107" t="str">
-        <v>P001</v>
-      </c>
-      <c r="G107" t="str">
-        <v>Laptop</v>
-      </c>
-      <c r="H107" t="str">
-        <v>Electronics</v>
-      </c>
-      <c r="I107">
-        <v>4</v>
-      </c>
-      <c r="J107">
-        <v>899.99</v>
-      </c>
-      <c r="K107" t="str">
-        <v>PayPal</v>
-      </c>
-      <c r="L107" t="str">
-        <v>Central</v>
-      </c>
-      <c r="M107" t="str">
-        <v>Basic</v>
-      </c>
-      <c r="N107" s="13">
-        <v>44734</v>
-      </c>
-      <c r="O107">
-        <v>3599.96</v>
-      </c>
-    </row>
-    <row r="108" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B108" t="str">
-        <v>TRX0188</v>
-      </c>
-      <c r="C108" s="13">
-        <v>45686</v>
-      </c>
-      <c r="D108" t="str">
-        <v>CUST201</v>
-      </c>
-      <c r="E108" t="str">
-        <v>Douglas Watson</v>
-      </c>
-      <c r="F108" t="str">
-        <v>P002</v>
-      </c>
-      <c r="G108" t="str">
-        <v>Smartphone</v>
-      </c>
-      <c r="H108" t="str">
-        <v>Electronics</v>
-      </c>
-      <c r="I108">
-        <v>2</v>
-      </c>
-      <c r="J108">
-        <v>699.99</v>
-      </c>
-      <c r="K108" t="str">
-        <v>Debit Card</v>
-      </c>
-      <c r="L108" t="str">
-        <v>Central</v>
-      </c>
-      <c r="M108" t="str">
-        <v>Premium</v>
-      </c>
-      <c r="N108" s="13">
-        <v>44681</v>
-      </c>
-      <c r="O108">
-        <v>1399.98</v>
-      </c>
-    </row>
-    <row r="109" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B109" t="str">
-        <v>TRX0010</v>
-      </c>
-      <c r="C109" s="13">
-        <v>45688</v>
-      </c>
-      <c r="D109" t="str">
-        <v>CUST202</v>
-      </c>
-      <c r="E109" t="str">
-        <v>Karen Hill</v>
-      </c>
-      <c r="F109" t="str">
-        <v>P002</v>
-      </c>
-      <c r="G109" t="str">
-        <v>Smartphone</v>
-      </c>
-      <c r="H109" t="str">
-        <v>Electronics</v>
-      </c>
-      <c r="I109">
-        <v>4</v>
-      </c>
-      <c r="J109">
-        <v>699.99</v>
-      </c>
-      <c r="K109" t="str">
-        <v>Debit Card</v>
-      </c>
-      <c r="L109" t="str">
-        <v>West</v>
-      </c>
-      <c r="M109" t="str">
-        <v>Premium</v>
-      </c>
-      <c r="N109" s="13">
-        <v>44692</v>
-      </c>
-      <c r="O109">
-        <v>2799.96</v>
-      </c>
-    </row>
-    <row r="110" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B110" t="str">
-        <v>TRX0069</v>
-      </c>
-      <c r="C110" s="13">
-        <v>45688</v>
-      </c>
-      <c r="D110" t="str">
-        <v>CUST203</v>
-      </c>
-      <c r="E110" t="str">
-        <v>Edward Mitchell</v>
-      </c>
-      <c r="F110" t="str">
-        <v>P010</v>
-      </c>
-      <c r="G110" t="str">
-        <v>Keyboard</v>
-      </c>
-      <c r="H110" t="str">
-        <v>Electronics</v>
-      </c>
-      <c r="I110">
-        <v>2</v>
-      </c>
-      <c r="J110">
-        <v>89.99</v>
-      </c>
-      <c r="K110" t="str">
-        <v>Debit Card</v>
-      </c>
-      <c r="L110" t="str">
-        <v>South</v>
-      </c>
-      <c r="M110" t="str">
-        <v>Basic</v>
-      </c>
-      <c r="N110" s="13">
-        <v>44777</v>
-      </c>
-      <c r="O110">
-        <v>179.98</v>
-      </c>
-    </row>
-    <row r="111" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B111" t="str">
-        <v>TRX0166</v>
-      </c>
-      <c r="C111" s="13">
-        <v>45688</v>
-      </c>
-      <c r="D111" t="str">
-        <v>CUST204</v>
-      </c>
-      <c r="E111" t="str">
-        <v>Michael Brown</v>
-      </c>
-      <c r="F111" t="str">
-        <v>P010</v>
-      </c>
-      <c r="G111" t="str">
-        <v>Keyboard</v>
-      </c>
-      <c r="H111" t="str">
-        <v>Electronics</v>
-      </c>
-      <c r="I111">
-        <v>3</v>
-      </c>
-      <c r="J111">
-        <v>89.99</v>
-      </c>
-      <c r="K111" t="str">
-        <v>Debit Card</v>
-      </c>
-      <c r="L111" t="str">
-        <v>South</v>
-      </c>
-      <c r="M111" t="str">
-        <v>Premium</v>
-      </c>
-      <c r="N111" s="13">
-        <v>45307</v>
-      </c>
-      <c r="O111">
-        <v>269.97000000000003</v>
-      </c>
-    </row>
-    <row r="112" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B112" t="str">
-        <v>TRX0196</v>
-      </c>
-      <c r="C112" s="13">
-        <v>45704</v>
-      </c>
-      <c r="D112" t="str">
-        <v>CUST211</v>
-      </c>
-      <c r="E112" t="str">
-        <v>Paul Baker</v>
-      </c>
-      <c r="F112" t="str">
-        <v>P010</v>
-      </c>
-      <c r="G112" t="str">
-        <v>Keyboard</v>
-      </c>
-      <c r="H112" t="str">
-        <v>Electronics</v>
-      </c>
-      <c r="I112">
-        <v>2</v>
-      </c>
-      <c r="J112">
-        <v>89.99</v>
-      </c>
-      <c r="K112" t="str">
-        <v>PayPal</v>
-      </c>
-      <c r="L112" t="str">
-        <v>Central</v>
-      </c>
-      <c r="M112" t="str">
-        <v>Basic</v>
-      </c>
-      <c r="N112" s="13">
-        <v>45257</v>
-      </c>
-      <c r="O112">
-        <v>179.98</v>
-      </c>
-    </row>
-    <row r="113" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B113" t="str">
-        <v>TRX0179</v>
-      </c>
-      <c r="C113" s="13">
-        <v>45707</v>
-      </c>
-      <c r="D113" t="str">
-        <v>CUST213</v>
-      </c>
-      <c r="E113" t="str">
-        <v>Edward Mitchell</v>
-      </c>
-      <c r="F113" t="str">
-        <v>P002</v>
-      </c>
-      <c r="G113" t="str">
-        <v>Smartphone</v>
-      </c>
-      <c r="H113" t="str">
-        <v>Electronics</v>
-      </c>
-      <c r="I113">
-        <v>5</v>
-      </c>
-      <c r="J113">
-        <v>699.99</v>
-      </c>
-      <c r="K113" t="str">
-        <v>PayPal</v>
-      </c>
-      <c r="L113" t="str">
-        <v>South</v>
-      </c>
-      <c r="M113" t="str">
-        <v>Premium</v>
-      </c>
-      <c r="N113" s="13">
-        <v>45352</v>
-      </c>
-      <c r="O113">
-        <v>3499.95</v>
-      </c>
-    </row>
-    <row r="114" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B114" t="str">
-        <v>TRX0214</v>
-      </c>
-      <c r="C114" s="13">
-        <v>45708</v>
-      </c>
-      <c r="D114" t="str">
-        <v>CUST215</v>
-      </c>
-      <c r="E114" t="str">
-        <v>Barbara Young</v>
-      </c>
-      <c r="F114" t="str">
-        <v>P001</v>
-      </c>
-      <c r="G114" t="str">
-        <v>Laptop</v>
-      </c>
-      <c r="H114" t="str">
-        <v>Electronics</v>
-      </c>
-      <c r="I114">
-        <v>3</v>
-      </c>
-      <c r="J114">
-        <v>899.99</v>
-      </c>
-      <c r="K114" t="str">
-        <v>Cash</v>
-      </c>
-      <c r="L114" t="str">
-        <v>East</v>
-      </c>
-      <c r="M114" t="str">
-        <v>Standard</v>
-      </c>
-      <c r="N114" s="13">
-        <v>44613</v>
-      </c>
-      <c r="O114">
-        <v>2699.97</v>
-      </c>
-    </row>
-    <row r="115" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B115" t="str">
-        <v>TRX0151</v>
-      </c>
-      <c r="C115" s="13">
-        <v>45710</v>
-      </c>
-      <c r="D115" t="str">
-        <v>CUST218</v>
-      </c>
-      <c r="E115" t="str">
-        <v>Sharon Butler</v>
-      </c>
-      <c r="F115" t="str">
-        <v>P002</v>
-      </c>
-      <c r="G115" t="str">
-        <v>Smartphone</v>
-      </c>
-      <c r="H115" t="str">
-        <v>Electronics</v>
-      </c>
-      <c r="I115">
-        <v>1</v>
-      </c>
-      <c r="J115">
-        <v>699.99</v>
-      </c>
-      <c r="K115" t="str">
-        <v>PayPal</v>
-      </c>
-      <c r="L115" t="str">
-        <v>West</v>
-      </c>
-      <c r="M115" t="str">
-        <v>Basic</v>
-      </c>
-      <c r="N115" s="13">
-        <v>44934</v>
-      </c>
-      <c r="O115">
-        <v>699.99</v>
-      </c>
-    </row>
-    <row r="116" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B116" t="str">
-        <v>TRX0047</v>
-      </c>
-      <c r="C116" s="13">
-        <v>45711</v>
-      </c>
-      <c r="D116" t="str">
-        <v>CUST219</v>
-      </c>
-      <c r="E116" t="str">
-        <v>Ruth Brooks</v>
-      </c>
-      <c r="F116" t="str">
-        <v>P002</v>
-      </c>
-      <c r="G116" t="str">
-        <v>Smartphone</v>
-      </c>
-      <c r="H116" t="str">
-        <v>Electronics</v>
-      </c>
-      <c r="I116">
-        <v>1</v>
-      </c>
-      <c r="J116">
-        <v>699.99</v>
-      </c>
-      <c r="K116" t="str">
-        <v>Cash</v>
-      </c>
-      <c r="L116" t="str">
-        <v>North</v>
-      </c>
-      <c r="M116" t="str">
-        <v>Premium</v>
-      </c>
-      <c r="N116" s="13">
-        <v>44583</v>
-      </c>
-      <c r="O116">
-        <v>699.99</v>
-      </c>
-    </row>
-    <row r="117" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B117" t="str">
-        <v>TRX0062</v>
-      </c>
-      <c r="C117" s="13">
-        <v>45711</v>
-      </c>
-      <c r="D117" t="str">
-        <v>CUST221</v>
-      </c>
-      <c r="E117" t="str">
-        <v>Elizabeth Hall</v>
-      </c>
-      <c r="F117" t="str">
-        <v>P010</v>
-      </c>
-      <c r="G117" t="str">
-        <v>Keyboard</v>
-      </c>
-      <c r="H117" t="str">
-        <v>Electronics</v>
-      </c>
-      <c r="I117">
-        <v>5</v>
-      </c>
-      <c r="J117">
-        <v>89.99</v>
-      </c>
-      <c r="K117" t="str">
-        <v>PayPal</v>
-      </c>
-      <c r="L117" t="str">
-        <v>West</v>
-      </c>
-      <c r="M117" t="str">
-        <v>Premium</v>
-      </c>
-      <c r="N117" s="13">
-        <v>45140</v>
-      </c>
-      <c r="O117">
-        <v>449.95</v>
-      </c>
-    </row>
-    <row r="118" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B118" t="str">
-        <v>TRX0226</v>
-      </c>
-      <c r="C118" s="13">
-        <v>45720</v>
-      </c>
-      <c r="D118" t="str">
-        <v>CUST226</v>
-      </c>
-      <c r="E118" t="str">
-        <v>Lawrence Reed</v>
-      </c>
-      <c r="F118" t="str">
-        <v>P002</v>
-      </c>
-      <c r="G118" t="str">
-        <v>Smartphone</v>
-      </c>
-      <c r="H118" t="str">
-        <v>Electronics</v>
-      </c>
-      <c r="I118">
-        <v>5</v>
-      </c>
-      <c r="J118">
-        <v>699.99</v>
-      </c>
-      <c r="K118" t="str">
-        <v>Debit Card</v>
-      </c>
-      <c r="L118" t="str">
-        <v>East</v>
-      </c>
-      <c r="M118" t="str">
-        <v>Premium</v>
-      </c>
-      <c r="N118" s="13">
-        <v>45161</v>
-      </c>
-      <c r="O118">
-        <v>3499.95</v>
-      </c>
-    </row>
-    <row r="119" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B119" t="str">
-        <v>TRX0233</v>
-      </c>
-      <c r="C119" s="13">
-        <v>45723</v>
-      </c>
-      <c r="D119" t="str">
-        <v>CUST228</v>
-      </c>
-      <c r="E119" t="str">
-        <v>Paul Baker</v>
-      </c>
-      <c r="F119" t="str">
-        <v>P010</v>
-      </c>
-      <c r="G119" t="str">
-        <v>Keyboard</v>
-      </c>
-      <c r="H119" t="str">
-        <v>Electronics</v>
-      </c>
-      <c r="I119">
-        <v>2</v>
-      </c>
-      <c r="J119">
-        <v>89.99</v>
-      </c>
-      <c r="K119" t="str">
-        <v>Credit Card</v>
-      </c>
-      <c r="L119" t="str">
-        <v>West</v>
-      </c>
-      <c r="M119" t="str">
-        <v>Premium</v>
-      </c>
-      <c r="N119" s="13">
-        <v>45295</v>
-      </c>
-      <c r="O119">
-        <v>179.98</v>
-      </c>
-    </row>
-    <row r="120" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B120" t="str">
-        <v>TRX0175</v>
-      </c>
-      <c r="C120" s="13">
-        <v>45723</v>
-      </c>
-      <c r="D120" t="str">
-        <v>CUST229</v>
-      </c>
-      <c r="E120" t="str">
-        <v>Helen Roberts</v>
-      </c>
-      <c r="F120" t="str">
-        <v>P009</v>
-      </c>
-      <c r="G120" t="str">
-        <v>Monitor</v>
-      </c>
-      <c r="H120" t="str">
-        <v>Electronics</v>
-      </c>
-      <c r="I120">
-        <v>5</v>
-      </c>
-      <c r="J120">
-        <v>249.99</v>
-      </c>
-      <c r="K120" t="str">
-        <v>Cash</v>
-      </c>
-      <c r="L120" t="str">
-        <v>East</v>
-      </c>
-      <c r="M120" t="str">
-        <v>Standard</v>
-      </c>
-      <c r="N120" s="13">
-        <v>44540</v>
-      </c>
-      <c r="O120">
-        <v>1249.95</v>
-      </c>
-    </row>
-    <row r="121" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B121" t="str">
-        <v>TRX0016</v>
-      </c>
-      <c r="C121" s="13">
-        <v>45724</v>
-      </c>
-      <c r="D121" t="str">
-        <v>CUST231</v>
-      </c>
-      <c r="E121" t="str">
-        <v>Harry Morgan</v>
-      </c>
-      <c r="F121" t="str">
-        <v>P001</v>
-      </c>
-      <c r="G121" t="str">
-        <v>Laptop</v>
-      </c>
-      <c r="H121" t="str">
-        <v>Electronics</v>
-      </c>
-      <c r="I121">
-        <v>5</v>
-      </c>
-      <c r="J121">
-        <v>899.99</v>
-      </c>
-      <c r="K121" t="str">
-        <v>PayPal</v>
-      </c>
-      <c r="L121" t="str">
-        <v>East</v>
-      </c>
-      <c r="M121" t="str">
-        <v>Premium</v>
-      </c>
-      <c r="N121" s="13">
-        <v>45389</v>
-      </c>
-      <c r="O121">
-        <v>4499.95</v>
-      </c>
-    </row>
-    <row r="122" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B122" t="str">
-        <v>TRX0038</v>
-      </c>
-      <c r="C122" s="13">
-        <v>45726</v>
-      </c>
-      <c r="D122" t="str">
-        <v>CUST233</v>
-      </c>
-      <c r="E122" t="str">
-        <v>Harry Morgan</v>
-      </c>
-      <c r="F122" t="str">
-        <v>P009</v>
-      </c>
-      <c r="G122" t="str">
-        <v>Monitor</v>
-      </c>
-      <c r="H122" t="str">
-        <v>Electronics</v>
-      </c>
-      <c r="I122">
-        <v>1</v>
-      </c>
-      <c r="J122">
-        <v>249.99</v>
-      </c>
-      <c r="K122" t="str">
-        <v>Cash</v>
-      </c>
-      <c r="L122" t="str">
-        <v>North</v>
-      </c>
-      <c r="M122" t="str">
-        <v>Standard</v>
-      </c>
-      <c r="N122" s="13">
-        <v>45117</v>
-      </c>
-      <c r="O122">
-        <v>249.99</v>
-      </c>
-    </row>
-    <row r="123" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B123" t="str">
-        <v>TRX0124</v>
-      </c>
-      <c r="C123" s="13">
-        <v>45737</v>
-      </c>
-      <c r="D123" t="str">
-        <v>CUST236</v>
-      </c>
-      <c r="E123" t="str">
-        <v>Sharon Butler</v>
-      </c>
-      <c r="F123" t="str">
-        <v>P001</v>
-      </c>
-      <c r="G123" t="str">
-        <v>Laptop</v>
-      </c>
-      <c r="H123" t="str">
-        <v>Electronics</v>
-      </c>
-      <c r="I123">
-        <v>3</v>
-      </c>
-      <c r="J123">
-        <v>899.99</v>
-      </c>
-      <c r="K123" t="str">
-        <v>Debit Card</v>
-      </c>
-      <c r="L123" t="str">
-        <v>North</v>
-      </c>
-      <c r="M123" t="str">
-        <v>Premium</v>
-      </c>
-      <c r="N123" s="13">
-        <v>44876</v>
-      </c>
-      <c r="O123">
-        <v>2699.97</v>
-      </c>
-    </row>
-    <row r="124" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B124" t="str">
-        <v>TRX0013</v>
-      </c>
-      <c r="C124" s="13">
-        <v>45737</v>
-      </c>
-      <c r="D124" t="str">
-        <v>CUST237</v>
-      </c>
-      <c r="E124" t="str">
-        <v>Dorothy Nelson</v>
-      </c>
-      <c r="F124" t="str">
-        <v>P001</v>
-      </c>
-      <c r="G124" t="str">
-        <v>Laptop</v>
-      </c>
-      <c r="H124" t="str">
-        <v>Electronics</v>
-      </c>
-      <c r="I124">
-        <v>3</v>
-      </c>
-      <c r="J124">
-        <v>899.99</v>
-      </c>
-      <c r="K124" t="str">
-        <v>PayPal</v>
-      </c>
-      <c r="L124" t="str">
-        <v>North</v>
-      </c>
-      <c r="M124" t="str">
-        <v>Basic</v>
-      </c>
-      <c r="N124" s="13">
-        <v>44975</v>
-      </c>
-      <c r="O124">
-        <v>2699.97</v>
-      </c>
-    </row>
-    <row r="125" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B125" t="str">
-        <v>TRX0213</v>
-      </c>
-      <c r="C125" s="13">
-        <v>45745</v>
-      </c>
-      <c r="D125" t="str">
-        <v>CUST241</v>
-      </c>
-      <c r="E125" t="str">
-        <v>Margaret Wright</v>
-      </c>
-      <c r="F125" t="str">
-        <v>P010</v>
-      </c>
-      <c r="G125" t="str">
-        <v>Keyboard</v>
-      </c>
-      <c r="H125" t="str">
-        <v>Electronics</v>
-      </c>
-      <c r="I125">
-        <v>5</v>
-      </c>
-      <c r="J125">
-        <v>89.99</v>
-      </c>
-      <c r="K125" t="str">
-        <v>PayPal</v>
-      </c>
-      <c r="L125" t="str">
-        <v>South</v>
-      </c>
-      <c r="M125" t="str">
-        <v>Basic</v>
-      </c>
-      <c r="N125" s="13">
-        <v>44704</v>
-      </c>
-      <c r="O125">
-        <v>449.95</v>
-      </c>
-    </row>
-    <row r="126" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B126" t="str">
-        <v>TRX0250</v>
-      </c>
-      <c r="C126" s="13">
-        <v>45746</v>
-      </c>
-      <c r="D126" t="str">
-        <v>CUST243</v>
-      </c>
-      <c r="E126" t="str">
-        <v>Karen Hill</v>
-      </c>
-      <c r="F126" t="str">
-        <v>P010</v>
-      </c>
-      <c r="G126" t="str">
-        <v>Keyboard</v>
-      </c>
-      <c r="H126" t="str">
-        <v>Electronics</v>
-      </c>
-      <c r="I126">
-        <v>2</v>
-      </c>
-      <c r="J126">
-        <v>89.99</v>
-      </c>
-      <c r="K126" t="str">
-        <v>Debit Card</v>
-      </c>
-      <c r="L126" t="str">
-        <v>West</v>
-      </c>
-      <c r="M126" t="str">
-        <v>Premium</v>
-      </c>
-      <c r="N126" s="13">
-        <v>44522</v>
-      </c>
-      <c r="O126">
-        <v>179.98</v>
-      </c>
-    </row>
-    <row r="127" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B127" t="str">
-        <v>TRX0068</v>
-      </c>
-      <c r="C127" s="13">
-        <v>45748</v>
-      </c>
-      <c r="D127" t="str">
-        <v>CUST244</v>
-      </c>
-      <c r="E127" t="str">
-        <v>Cynthia Price</v>
-      </c>
-      <c r="F127" t="str">
-        <v>P002</v>
-      </c>
-      <c r="G127" t="str">
-        <v>Smartphone</v>
-      </c>
-      <c r="H127" t="str">
-        <v>Electronics</v>
-      </c>
-      <c r="I127">
-        <v>2</v>
-      </c>
-      <c r="J127">
-        <v>699.99</v>
-      </c>
-      <c r="K127" t="str">
-        <v>PayPal</v>
-      </c>
-      <c r="L127" t="str">
-        <v>North</v>
-      </c>
-      <c r="M127" t="str">
-        <v>Standard</v>
-      </c>
-      <c r="N127" s="13">
-        <v>44618</v>
-      </c>
-      <c r="O127">
-        <v>1399.98</v>
-      </c>
-    </row>
-    <row r="128" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B128" t="str">
-        <v>TRX0144</v>
-      </c>
-      <c r="C128" s="13">
-        <v>45749</v>
-      </c>
-      <c r="D128" t="str">
-        <v>CUST245</v>
-      </c>
-      <c r="E128" t="str">
-        <v>Edward Mitchell</v>
-      </c>
-      <c r="F128" t="str">
-        <v>P001</v>
-      </c>
-      <c r="G128" t="str">
-        <v>Laptop</v>
-      </c>
-      <c r="H128" t="str">
-        <v>Electronics</v>
-      </c>
-      <c r="I128">
-        <v>3</v>
-      </c>
-      <c r="J128">
-        <v>899.99</v>
-      </c>
-      <c r="K128" t="str">
-        <v>Cash</v>
-      </c>
-      <c r="L128" t="str">
-        <v>Central</v>
-      </c>
-      <c r="M128" t="str">
-        <v>Standard</v>
-      </c>
-      <c r="N128" s="13">
-        <v>44953</v>
-      </c>
-      <c r="O128">
-        <v>2699.97</v>
-      </c>
-    </row>
-    <row r="129" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B129" t="str">
-        <v>TRX0116</v>
-      </c>
-      <c r="C129" s="13">
-        <v>45756</v>
-      </c>
-      <c r="D129" t="str">
-        <v>CUST247</v>
-      </c>
-      <c r="E129" t="str">
-        <v>Robert Thomas</v>
-      </c>
-      <c r="F129" t="str">
-        <v>P010</v>
-      </c>
-      <c r="G129" t="str">
-        <v>Keyboard</v>
-      </c>
-      <c r="H129" t="str">
-        <v>Electronics</v>
-      </c>
-      <c r="I129">
-        <v>1</v>
-      </c>
-      <c r="J129">
-        <v>89.99</v>
-      </c>
-      <c r="K129" t="str">
-        <v>Debit Card</v>
-      </c>
-      <c r="L129" t="str">
-        <v>East</v>
-      </c>
-      <c r="M129" t="str">
-        <v>Basic</v>
-      </c>
-      <c r="N129" s="13">
-        <v>45346</v>
-      </c>
-      <c r="O129">
-        <v>89.99</v>
-      </c>
-    </row>
-    <row r="130" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B130" t="str">
-        <v>TRX0120</v>
-      </c>
-      <c r="C130" s="13">
-        <v>45758</v>
-      </c>
-      <c r="D130" t="str">
-        <v>CUST248</v>
-      </c>
-      <c r="E130" t="str">
-        <v>Douglas Watson</v>
-      </c>
-      <c r="F130" t="str">
-        <v>P002</v>
-      </c>
-      <c r="G130" t="str">
-        <v>Smartphone</v>
-      </c>
-      <c r="H130" t="str">
-        <v>Electronics</v>
-      </c>
-      <c r="I130">
-        <v>3</v>
-      </c>
-      <c r="J130">
-        <v>699.99</v>
-      </c>
-      <c r="K130" t="str">
-        <v>PayPal</v>
-      </c>
-      <c r="L130" t="str">
-        <v>North</v>
-      </c>
-      <c r="M130" t="str">
-        <v>Basic</v>
-      </c>
-      <c r="N130" s="13">
-        <v>44909</v>
-      </c>
-      <c r="O130">
-        <v>2099.9699999999998</v>
-      </c>
-    </row>
-    <row r="131" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B131" t="str">
-        <v>TRX0103</v>
-      </c>
-      <c r="C131" s="13">
-        <v>45758</v>
-      </c>
-      <c r="D131" t="str">
-        <v>CUST249</v>
-      </c>
-      <c r="E131" t="str">
-        <v>Lawrence Reed</v>
-      </c>
-      <c r="F131" t="str">
-        <v>P010</v>
-      </c>
-      <c r="G131" t="str">
-        <v>Keyboard</v>
-      </c>
-      <c r="H131" t="str">
-        <v>Electronics</v>
-      </c>
-      <c r="I131">
-        <v>2</v>
-      </c>
-      <c r="J131">
-        <v>89.99</v>
-      </c>
-      <c r="K131" t="str">
-        <v>Debit Card</v>
-      </c>
-      <c r="L131" t="str">
-        <v>East</v>
-      </c>
-      <c r="M131" t="str">
-        <v>Basic</v>
-      </c>
-      <c r="N131" s="13">
-        <v>45088</v>
-      </c>
-      <c r="O131">
-        <v>179.98</v>
-      </c>
-    </row>
-    <row r="132" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B132" t="str">
-        <v>TRX0064</v>
-      </c>
-      <c r="C132" s="13">
-        <v>45758</v>
-      </c>
-      <c r="D132" t="str">
-        <v>CUST250</v>
-      </c>
-      <c r="E132" t="str">
-        <v>Steven Turner</v>
-      </c>
-      <c r="F132" t="str">
-        <v>P010</v>
-      </c>
-      <c r="G132" t="str">
-        <v>Keyboard</v>
-      </c>
-      <c r="H132" t="str">
-        <v>Electronics</v>
-      </c>
-      <c r="I132">
-        <v>3</v>
-      </c>
-      <c r="J132">
-        <v>89.99</v>
-      </c>
-      <c r="K132" t="str">
-        <v>Debit Card</v>
-      </c>
-      <c r="L132" t="str">
-        <v>North</v>
-      </c>
-      <c r="M132" t="str">
-        <v>Premium</v>
-      </c>
-      <c r="N132" s="13">
-        <v>44878</v>
-      </c>
-      <c r="O132">
-        <v>269.97000000000003</v>
       </c>
     </row>
   </sheetData>
@@ -69955,232 +67477,208 @@
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B4" s="29" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4">
-        <v>41288.340000000018</v>
+        <v>37</v>
+      </c>
+      <c r="C4" s="33">
+        <v>50808.31</v>
       </c>
       <c r="E4" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="F4">
-        <v>8338.7399999999961</v>
+      <c r="F4" s="33">
+        <v>1119.8399999999999</v>
       </c>
       <c r="H4" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="I4">
-        <v>5219.1299999999974</v>
+      <c r="I4" s="33">
+        <v>479.92</v>
       </c>
       <c r="K4" s="29" t="s">
         <v>662</v>
       </c>
-      <c r="L4">
-        <v>25799.15</v>
+      <c r="L4" s="33">
+        <v>4599.8899999999994</v>
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B5" s="29" t="s">
-        <v>56</v>
-      </c>
-      <c r="C5">
-        <v>59288.389999999992</v>
+        <v>658</v>
+      </c>
+      <c r="C5" s="33">
+        <v>50808.31</v>
       </c>
       <c r="E5" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="F5">
-        <v>171756.05000000013</v>
+      <c r="F5" s="33">
+        <v>39239.040000000008</v>
       </c>
       <c r="H5" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="I5">
-        <v>15298.979999999994</v>
+      <c r="I5" s="33">
+        <v>4949.67</v>
       </c>
       <c r="K5" s="29" t="s">
         <v>663</v>
       </c>
-      <c r="L5">
-        <v>16069.379999999997</v>
+      <c r="L5" s="33">
+        <v>1749.92</v>
       </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B6" s="29" t="s">
-        <v>37</v>
-      </c>
-      <c r="C6">
-        <v>50808.310000000012</v>
-      </c>
       <c r="E6" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="F6">
-        <v>49097.680000000015</v>
+      <c r="F6" s="33">
+        <v>10449.429999999998</v>
       </c>
       <c r="H6" s="29" t="s">
         <v>94</v>
       </c>
-      <c r="I6">
-        <v>3119.6099999999992</v>
+      <c r="I6" s="33">
+        <v>639.91999999999996</v>
       </c>
       <c r="K6" s="29" t="s">
         <v>664</v>
       </c>
-      <c r="L6">
-        <v>19899.379999999997</v>
+      <c r="L6" s="33">
+        <v>5649.9299999999994</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B7" s="29" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7">
-        <v>36398.750000000007</v>
-      </c>
       <c r="E7" s="29" t="s">
         <v>658</v>
       </c>
-      <c r="F7">
-        <v>229192.47000000015</v>
+      <c r="F7" s="33">
+        <v>50808.310000000005</v>
       </c>
       <c r="H7" s="29" t="s">
         <v>87</v>
       </c>
-      <c r="I7">
-        <v>23399.22</v>
+      <c r="I7" s="33">
+        <v>2099.9300000000003</v>
       </c>
       <c r="K7" s="29" t="s">
         <v>665</v>
       </c>
-      <c r="L7">
-        <v>27899.160000000007</v>
+      <c r="L7" s="33">
+        <v>9969.5999999999985</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B8" s="29" t="s">
-        <v>45</v>
-      </c>
-      <c r="C8">
-        <v>41408.680000000015</v>
-      </c>
       <c r="H8" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="I8">
-        <v>7049.5299999999988</v>
+      <c r="I8" s="33">
+        <v>1949.8700000000001</v>
       </c>
       <c r="K8" s="29" t="s">
         <v>666</v>
       </c>
-      <c r="L8">
-        <v>17039.349999999999</v>
+      <c r="L8" s="33">
+        <v>2129.87</v>
       </c>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B9" s="29" t="s">
-        <v>658</v>
-      </c>
-      <c r="C9">
-        <v>229192.47000000006</v>
-      </c>
       <c r="H9" s="29" t="s">
         <v>97</v>
       </c>
-      <c r="I9">
-        <v>8009.1099999999969</v>
+      <c r="I9" s="33">
+        <v>1889.7900000000002</v>
       </c>
       <c r="K9" s="29" t="s">
         <v>667</v>
       </c>
-      <c r="L9">
-        <v>19299.45</v>
+      <c r="L9" s="33">
+        <v>89.99</v>
       </c>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.3">
       <c r="H10" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="I10">
-        <v>67499.25</v>
+      <c r="I10" s="33">
+        <v>12599.859999999999</v>
       </c>
       <c r="K10" s="29" t="s">
         <v>668</v>
       </c>
-      <c r="L10">
-        <v>18479.399999999994</v>
+      <c r="L10" s="33">
+        <v>3919.8199999999997</v>
       </c>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.3">
       <c r="H11" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="I11">
-        <v>21999.119999999999</v>
+      <c r="I11" s="33">
+        <v>5999.76</v>
       </c>
       <c r="K11" s="29" t="s">
         <v>669</v>
       </c>
-      <c r="L11">
-        <v>15759.429999999997</v>
+      <c r="L11" s="33">
+        <v>5539.8</v>
       </c>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.3">
       <c r="H12" s="29" t="s">
         <v>104</v>
       </c>
-      <c r="I12">
-        <v>10399.479999999998</v>
+      <c r="I12" s="33">
+        <v>3399.8300000000004</v>
       </c>
       <c r="K12" s="29" t="s">
         <v>670</v>
       </c>
-      <c r="L12">
-        <v>12989.509999999997</v>
+      <c r="L12" s="33">
+        <v>3869.88</v>
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.3">
       <c r="H13" s="29" t="s">
         <v>69</v>
       </c>
-      <c r="I13">
-        <v>67199.039999999994</v>
+      <c r="I13" s="33">
+        <v>16799.759999999998</v>
       </c>
       <c r="K13" s="29" t="s">
         <v>671</v>
       </c>
-      <c r="L13">
-        <v>20609.52</v>
+      <c r="L13" s="33">
+        <v>4369.88</v>
       </c>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="H14" s="29" t="s">
         <v>658</v>
       </c>
-      <c r="I14">
-        <v>229192.46999999997</v>
+      <c r="I14" s="33">
+        <v>50808.31</v>
       </c>
       <c r="K14" s="29" t="s">
         <v>672</v>
       </c>
-      <c r="L14">
-        <v>12309.439999999999</v>
+      <c r="L14" s="33">
+        <v>2969.83</v>
       </c>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="K15" s="29" t="s">
         <v>673</v>
       </c>
-      <c r="L15">
-        <v>23039.3</v>
+      <c r="L15" s="33">
+        <v>5949.9</v>
       </c>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.3">
       <c r="K16" s="29" t="s">
         <v>658</v>
       </c>
-      <c r="L16">
-        <v>229192.47</v>
+      <c r="L16" s="33">
+        <v>50808.31</v>
       </c>
     </row>
   </sheetData>
